--- a/almacenes/LZA_ubicaciones.xlsx
+++ b/almacenes/LZA_ubicaciones.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12310" uniqueCount="3154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12119" uniqueCount="3147">
   <si>
     <t>ALMACEN</t>
   </si>
@@ -9071,12 +9071,6 @@
     <t>P2E1</t>
   </si>
   <si>
-    <t>ENTREGAS</t>
-  </si>
-  <si>
-    <t>_</t>
-  </si>
-  <si>
     <t>P17E1</t>
   </si>
   <si>
@@ -9455,28 +9449,13 @@
     <t>P15E1</t>
   </si>
   <si>
-    <t>P16E2</t>
-  </si>
-  <si>
-    <t>P16E1</t>
-  </si>
-  <si>
     <t>P16E7</t>
   </si>
   <si>
-    <t>P16E6</t>
-  </si>
-  <si>
-    <t>P16E5</t>
-  </si>
-  <si>
-    <t>P16E4</t>
-  </si>
-  <si>
-    <t>P16E3</t>
-  </si>
-  <si>
     <t>MUELLE</t>
+  </si>
+  <si>
+    <t>ENTREGA</t>
   </si>
 </sst>
 </file>
@@ -9568,7 +9547,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -9581,6 +9560,21 @@
     </xf>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -60780,1095 +60774,2509 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:AO58"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="38" width="3.625" customWidth="1"/>
+    <col min="39" max="39" width="3.5" customWidth="1"/>
+    <col min="40" max="167" width="3.625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:14">
-      <c r="A1" t="s">
+    <row r="1" spans="1:41">
+      <c r="A1" s="6"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="R1" s="8" t="s">
+        <v>3144</v>
+      </c>
+      <c r="S1" s="8"/>
+      <c r="T1" s="8"/>
+      <c r="U1" s="8" t="s">
+        <v>3144</v>
+      </c>
+      <c r="V1" s="8"/>
+      <c r="W1" s="8"/>
+      <c r="X1" s="8" t="s">
+        <v>3144</v>
+      </c>
+      <c r="Y1" s="8"/>
+      <c r="Z1" s="8"/>
+      <c r="AA1" s="8" t="s">
+        <v>3144</v>
+      </c>
+      <c r="AB1" s="8"/>
+      <c r="AC1" s="8"/>
+      <c r="AD1" s="8" t="s">
+        <v>3144</v>
+      </c>
+      <c r="AE1" s="8"/>
+      <c r="AF1" s="8"/>
+      <c r="AG1" s="8" t="s">
+        <v>3144</v>
+      </c>
+      <c r="AH1" s="8"/>
+      <c r="AI1" s="8"/>
+      <c r="AJ1" s="8" t="s">
+        <v>3144</v>
+      </c>
+      <c r="AK1" s="8"/>
+      <c r="AL1" s="8"/>
+    </row>
+    <row r="2" spans="1:41">
+      <c r="A2" s="6"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="R2" s="8"/>
+      <c r="S2" s="8"/>
+      <c r="T2" s="8"/>
+      <c r="U2" s="8"/>
+      <c r="V2" s="8"/>
+      <c r="W2" s="8"/>
+      <c r="X2" s="8"/>
+      <c r="Y2" s="8"/>
+      <c r="Z2" s="8"/>
+      <c r="AA2" s="8"/>
+      <c r="AB2" s="8"/>
+      <c r="AC2" s="8"/>
+      <c r="AD2" s="8"/>
+      <c r="AE2" s="8"/>
+      <c r="AF2" s="8"/>
+      <c r="AG2" s="8"/>
+      <c r="AH2" s="8"/>
+      <c r="AI2" s="8"/>
+      <c r="AJ2" s="8"/>
+      <c r="AK2" s="8"/>
+      <c r="AL2" s="8"/>
+    </row>
+    <row r="3" spans="1:41">
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+      <c r="U3" s="6"/>
+      <c r="V3" s="6"/>
+      <c r="W3" s="6"/>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="6"/>
+      <c r="Z3" s="6"/>
+      <c r="AA3" s="6"/>
+      <c r="AB3" s="6"/>
+      <c r="AC3" s="6"/>
+      <c r="AD3" s="6"/>
+      <c r="AE3" s="6"/>
+      <c r="AF3" s="6"/>
+      <c r="AG3" s="6"/>
+      <c r="AH3" s="6"/>
+      <c r="AI3" s="6"/>
+      <c r="AJ3" s="6"/>
+      <c r="AK3" s="6"/>
+      <c r="AL3" s="6"/>
+      <c r="AM3" s="6"/>
+      <c r="AN3" s="8" t="s">
         <v>3019</v>
       </c>
-      <c r="B1" t="s">
-        <v>3019</v>
-      </c>
-      <c r="C1" t="s">
-        <v>3019</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3019</v>
-      </c>
-      <c r="E1" t="s">
-        <v>3019</v>
-      </c>
-      <c r="F1" t="s">
-        <v>3019</v>
-      </c>
-      <c r="G1" t="s">
-        <v>3148</v>
-      </c>
-      <c r="H1" t="s">
-        <v>3149</v>
-      </c>
-      <c r="I1" t="s">
-        <v>3150</v>
-      </c>
-      <c r="J1" t="s">
-        <v>3151</v>
-      </c>
-      <c r="K1" t="s">
-        <v>3152</v>
-      </c>
-      <c r="L1" t="s">
+      <c r="AO3" s="8"/>
+    </row>
+    <row r="4" spans="1:41">
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="8" t="s">
+        <v>3145</v>
+      </c>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6"/>
+      <c r="U4" s="6"/>
+      <c r="V4" s="6"/>
+      <c r="W4" s="6"/>
+      <c r="X4" s="6"/>
+      <c r="Y4" s="6"/>
+      <c r="Z4" s="6"/>
+      <c r="AA4" s="6"/>
+      <c r="AB4" s="6"/>
+      <c r="AC4" s="6"/>
+      <c r="AD4" s="6"/>
+      <c r="AE4" s="6"/>
+      <c r="AF4" s="6"/>
+      <c r="AG4" s="6"/>
+      <c r="AH4" s="6"/>
+      <c r="AI4" s="6"/>
+      <c r="AJ4" s="6"/>
+      <c r="AK4" s="6"/>
+      <c r="AL4" s="6"/>
+      <c r="AM4" s="6"/>
+      <c r="AN4" s="8"/>
+      <c r="AO4" s="8"/>
+    </row>
+    <row r="5" spans="1:41">
+      <c r="A5" s="6"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="6"/>
+      <c r="R5" s="5"/>
+      <c r="S5" s="5"/>
+      <c r="T5" s="5"/>
+      <c r="U5" s="5"/>
+      <c r="V5" s="5"/>
+      <c r="W5" s="5"/>
+      <c r="X5" s="5"/>
+      <c r="Y5" s="5"/>
+      <c r="Z5" s="5"/>
+      <c r="AA5" s="5"/>
+      <c r="AB5" s="5"/>
+      <c r="AC5" s="5"/>
+      <c r="AD5" s="5"/>
+      <c r="AE5" s="5"/>
+      <c r="AF5" s="5"/>
+      <c r="AG5" s="5"/>
+      <c r="AH5" s="5"/>
+      <c r="AI5" s="5"/>
+      <c r="AJ5" s="5"/>
+      <c r="AK5" s="6"/>
+      <c r="AL5" s="5"/>
+      <c r="AM5" s="5"/>
+      <c r="AN5" s="8"/>
+      <c r="AO5" s="8"/>
+    </row>
+    <row r="6" spans="1:41">
+      <c r="A6" s="6"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="6"/>
+      <c r="R6" s="5"/>
+      <c r="S6" s="5"/>
+      <c r="T6" s="5"/>
+      <c r="U6" s="5"/>
+      <c r="V6" s="5"/>
+      <c r="W6" s="5"/>
+      <c r="X6" s="5"/>
+      <c r="Y6" s="5"/>
+      <c r="Z6" s="5"/>
+      <c r="AA6" s="5"/>
+      <c r="AB6" s="5"/>
+      <c r="AC6" s="5"/>
+      <c r="AD6" s="5"/>
+      <c r="AE6" s="5"/>
+      <c r="AF6" s="5"/>
+      <c r="AG6" s="5"/>
+      <c r="AH6" s="5"/>
+      <c r="AI6" s="5"/>
+      <c r="AJ6" s="5"/>
+      <c r="AK6" s="6"/>
+      <c r="AL6" s="5"/>
+      <c r="AM6" s="5"/>
+      <c r="AN6" s="8" t="s">
+        <v>3020</v>
+      </c>
+      <c r="AO6" s="8"/>
+    </row>
+    <row r="7" spans="1:41" ht="14.25" customHeight="1">
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="6"/>
+      <c r="R7" s="7"/>
+      <c r="S7" s="8" t="s">
+        <v>3138</v>
+      </c>
+      <c r="T7" s="8"/>
+      <c r="U7" s="8"/>
+      <c r="V7" s="8" t="s">
+        <v>3139</v>
+      </c>
+      <c r="W7" s="8"/>
+      <c r="X7" s="8"/>
+      <c r="Y7" s="8" t="s">
+        <v>3140</v>
+      </c>
+      <c r="Z7" s="8"/>
+      <c r="AA7" s="8"/>
+      <c r="AB7" s="8" t="s">
+        <v>3141</v>
+      </c>
+      <c r="AC7" s="8"/>
+      <c r="AD7" s="8"/>
+      <c r="AE7" s="8" t="s">
+        <v>3142</v>
+      </c>
+      <c r="AF7" s="8"/>
+      <c r="AG7" s="8"/>
+      <c r="AH7" s="8" t="s">
+        <v>3143</v>
+      </c>
+      <c r="AI7" s="8"/>
+      <c r="AJ7" s="8"/>
+      <c r="AK7" s="6"/>
+      <c r="AN7" s="8"/>
+      <c r="AO7" s="8"/>
+    </row>
+    <row r="8" spans="1:41">
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="6"/>
+      <c r="Q8" s="9" t="s">
+        <v>3104</v>
+      </c>
+      <c r="R8" s="8"/>
+      <c r="S8" s="8"/>
+      <c r="T8" s="8"/>
+      <c r="U8" s="8"/>
+      <c r="V8" s="8"/>
+      <c r="W8" s="8"/>
+      <c r="X8" s="8"/>
+      <c r="Y8" s="8"/>
+      <c r="Z8" s="8"/>
+      <c r="AA8" s="8"/>
+      <c r="AB8" s="8"/>
+      <c r="AC8" s="8"/>
+      <c r="AD8" s="8"/>
+      <c r="AE8" s="8"/>
+      <c r="AF8" s="8"/>
+      <c r="AG8" s="8"/>
+      <c r="AH8" s="8"/>
+      <c r="AI8" s="8"/>
+      <c r="AJ8" s="8"/>
+      <c r="AK8" s="6"/>
+      <c r="AL8" s="5"/>
+      <c r="AM8" s="5"/>
+      <c r="AN8" s="8"/>
+      <c r="AO8" s="8"/>
+    </row>
+    <row r="9" spans="1:41">
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="6"/>
+      <c r="Q9" s="9"/>
+      <c r="R9" s="8"/>
+      <c r="S9" s="8" t="s">
+        <v>3132</v>
+      </c>
+      <c r="T9" s="8"/>
+      <c r="U9" s="8"/>
+      <c r="V9" s="8" t="s">
+        <v>3133</v>
+      </c>
+      <c r="W9" s="8"/>
+      <c r="X9" s="8"/>
+      <c r="Y9" s="8" t="s">
+        <v>3134</v>
+      </c>
+      <c r="Z9" s="8"/>
+      <c r="AA9" s="8"/>
+      <c r="AB9" s="8" t="s">
+        <v>3135</v>
+      </c>
+      <c r="AC9" s="8"/>
+      <c r="AD9" s="8"/>
+      <c r="AE9" s="8" t="s">
+        <v>3136</v>
+      </c>
+      <c r="AF9" s="8"/>
+      <c r="AG9" s="8"/>
+      <c r="AH9" s="8" t="s">
+        <v>3137</v>
+      </c>
+      <c r="AI9" s="8"/>
+      <c r="AJ9" s="8"/>
+      <c r="AK9" s="6"/>
+      <c r="AL9" s="5"/>
+      <c r="AM9" s="5"/>
+      <c r="AN9" s="8" t="s">
+        <v>3021</v>
+      </c>
+      <c r="AO9" s="8"/>
+    </row>
+    <row r="10" spans="1:41">
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="6"/>
+      <c r="Q10" s="9"/>
+      <c r="R10" s="8"/>
+      <c r="S10" s="8"/>
+      <c r="T10" s="8"/>
+      <c r="U10" s="8"/>
+      <c r="V10" s="8"/>
+      <c r="W10" s="8"/>
+      <c r="X10" s="8"/>
+      <c r="Y10" s="8"/>
+      <c r="Z10" s="8"/>
+      <c r="AA10" s="8"/>
+      <c r="AB10" s="8"/>
+      <c r="AC10" s="8"/>
+      <c r="AD10" s="8"/>
+      <c r="AE10" s="8"/>
+      <c r="AF10" s="8"/>
+      <c r="AG10" s="8"/>
+      <c r="AH10" s="8"/>
+      <c r="AI10" s="8"/>
+      <c r="AJ10" s="8"/>
+      <c r="AK10" s="6"/>
+      <c r="AL10" s="5"/>
+      <c r="AM10" s="5"/>
+      <c r="AN10" s="8"/>
+      <c r="AO10" s="8"/>
+    </row>
+    <row r="11" spans="1:41">
+      <c r="A11" s="6"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="6"/>
+      <c r="Q11" s="8" t="s">
+        <v>3105</v>
+      </c>
+      <c r="R11" s="8"/>
+      <c r="S11" s="6"/>
+      <c r="T11" s="6"/>
+      <c r="U11" s="6"/>
+      <c r="V11" s="6"/>
+      <c r="W11" s="6"/>
+      <c r="X11" s="6"/>
+      <c r="Y11" s="6"/>
+      <c r="Z11" s="6"/>
+      <c r="AA11" s="6"/>
+      <c r="AB11" s="6"/>
+      <c r="AC11" s="6"/>
+      <c r="AD11" s="6"/>
+      <c r="AE11" s="6"/>
+      <c r="AF11" s="6"/>
+      <c r="AG11" s="6"/>
+      <c r="AH11" s="6"/>
+      <c r="AI11" s="6"/>
+      <c r="AJ11" s="6"/>
+      <c r="AK11" s="6"/>
+      <c r="AL11" s="6"/>
+      <c r="AM11" s="6"/>
+      <c r="AN11" s="8"/>
+      <c r="AO11" s="8"/>
+    </row>
+    <row r="12" spans="1:41">
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="6"/>
+      <c r="Q12" s="8"/>
+      <c r="R12" s="8"/>
+      <c r="S12" s="9" t="s">
+        <v>3126</v>
+      </c>
+      <c r="T12" s="9"/>
+      <c r="U12" s="9"/>
+      <c r="V12" s="9" t="s">
+        <v>3127</v>
+      </c>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="9" t="s">
+        <v>3128</v>
+      </c>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
+      <c r="AB12" s="9" t="s">
+        <v>3129</v>
+      </c>
+      <c r="AC12" s="9"/>
+      <c r="AD12" s="9"/>
+      <c r="AE12" s="8" t="s">
+        <v>3130</v>
+      </c>
+      <c r="AF12" s="8"/>
+      <c r="AG12" s="8"/>
+      <c r="AH12" s="9" t="s">
+        <v>3131</v>
+      </c>
+      <c r="AI12" s="9"/>
+      <c r="AJ12" s="9"/>
+      <c r="AK12" s="7"/>
+      <c r="AN12" s="8" t="s">
+        <v>3022</v>
+      </c>
+      <c r="AO12" s="8"/>
+    </row>
+    <row r="13" spans="1:41" ht="14.25" customHeight="1">
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="8"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="6"/>
+      <c r="Q13" s="8"/>
+      <c r="R13" s="8"/>
+      <c r="S13" s="9"/>
+      <c r="T13" s="9"/>
+      <c r="U13" s="9"/>
+      <c r="V13" s="9"/>
+      <c r="W13" s="9"/>
+      <c r="X13" s="9"/>
+      <c r="Y13" s="9"/>
+      <c r="Z13" s="9"/>
+      <c r="AA13" s="9"/>
+      <c r="AB13" s="9"/>
+      <c r="AC13" s="9"/>
+      <c r="AD13" s="9"/>
+      <c r="AE13" s="8"/>
+      <c r="AF13" s="8"/>
+      <c r="AG13" s="8"/>
+      <c r="AH13" s="9"/>
+      <c r="AI13" s="9"/>
+      <c r="AJ13" s="9"/>
+      <c r="AK13" s="7"/>
+      <c r="AL13" s="5"/>
+      <c r="AM13" s="5"/>
+      <c r="AN13" s="8"/>
+      <c r="AO13" s="8"/>
+    </row>
+    <row r="14" spans="1:41">
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="6"/>
+      <c r="Q14" s="8" t="s">
+        <v>3106</v>
+      </c>
+      <c r="R14" s="8"/>
+      <c r="S14" s="8" t="s">
+        <v>3120</v>
+      </c>
+      <c r="T14" s="8"/>
+      <c r="U14" s="8"/>
+      <c r="V14" s="8" t="s">
+        <v>3121</v>
+      </c>
+      <c r="W14" s="8"/>
+      <c r="X14" s="8"/>
+      <c r="Y14" s="8" t="s">
+        <v>3122</v>
+      </c>
+      <c r="Z14" s="8"/>
+      <c r="AA14" s="8"/>
+      <c r="AB14" s="8" t="s">
+        <v>3123</v>
+      </c>
+      <c r="AC14" s="8"/>
+      <c r="AD14" s="8"/>
+      <c r="AE14" s="8" t="s">
+        <v>3124</v>
+      </c>
+      <c r="AF14" s="8"/>
+      <c r="AG14" s="8"/>
+      <c r="AH14" s="8" t="s">
+        <v>3125</v>
+      </c>
+      <c r="AI14" s="8"/>
+      <c r="AJ14" s="8"/>
+      <c r="AK14" s="6"/>
+      <c r="AL14" s="5"/>
+      <c r="AM14" s="5"/>
+      <c r="AN14" s="8"/>
+      <c r="AO14" s="8"/>
+    </row>
+    <row r="15" spans="1:41">
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="8"/>
+      <c r="M15" s="6"/>
+      <c r="Q15" s="8"/>
+      <c r="R15" s="8"/>
+      <c r="S15" s="8"/>
+      <c r="T15" s="8"/>
+      <c r="U15" s="8"/>
+      <c r="V15" s="8"/>
+      <c r="W15" s="8"/>
+      <c r="X15" s="8"/>
+      <c r="Y15" s="8"/>
+      <c r="Z15" s="8"/>
+      <c r="AA15" s="8"/>
+      <c r="AB15" s="8"/>
+      <c r="AC15" s="8"/>
+      <c r="AD15" s="8"/>
+      <c r="AE15" s="8"/>
+      <c r="AF15" s="8"/>
+      <c r="AG15" s="8"/>
+      <c r="AH15" s="8"/>
+      <c r="AI15" s="8"/>
+      <c r="AJ15" s="8"/>
+      <c r="AK15" s="6"/>
+      <c r="AL15" s="5"/>
+      <c r="AM15" s="5"/>
+      <c r="AN15" s="8" t="s">
+        <v>3023</v>
+      </c>
+      <c r="AO15" s="8"/>
+    </row>
+    <row r="16" spans="1:41">
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="6"/>
+      <c r="Q16" s="8"/>
+      <c r="R16" s="8"/>
+      <c r="S16" s="5"/>
+      <c r="T16" s="5"/>
+      <c r="U16" s="5"/>
+      <c r="V16" s="5"/>
+      <c r="W16" s="5"/>
+      <c r="X16" s="5"/>
+      <c r="Y16" s="5"/>
+      <c r="Z16" s="5"/>
+      <c r="AA16" s="5"/>
+      <c r="AB16" s="5"/>
+      <c r="AC16" s="5"/>
+      <c r="AD16" s="5"/>
+      <c r="AE16" s="5"/>
+      <c r="AF16" s="5"/>
+      <c r="AG16" s="5"/>
+      <c r="AH16" s="5"/>
+      <c r="AI16" s="5"/>
+      <c r="AJ16" s="5"/>
+      <c r="AK16" s="6"/>
+      <c r="AL16" s="5"/>
+      <c r="AM16" s="5"/>
+      <c r="AN16" s="8"/>
+      <c r="AO16" s="8"/>
+    </row>
+    <row r="17" spans="1:41">
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="6"/>
+      <c r="Q17" s="8" t="s">
+        <v>3107</v>
+      </c>
+      <c r="R17" s="8"/>
+      <c r="S17" s="9" t="s">
+        <v>3114</v>
+      </c>
+      <c r="T17" s="9"/>
+      <c r="U17" s="9"/>
+      <c r="V17" s="9" t="s">
+        <v>3115</v>
+      </c>
+      <c r="W17" s="9"/>
+      <c r="X17" s="9"/>
+      <c r="Y17" s="9" t="s">
+        <v>3116</v>
+      </c>
+      <c r="Z17" s="9"/>
+      <c r="AA17" s="9"/>
+      <c r="AB17" s="9" t="s">
+        <v>3117</v>
+      </c>
+      <c r="AC17" s="9"/>
+      <c r="AD17" s="9"/>
+      <c r="AE17" s="8" t="s">
+        <v>3118</v>
+      </c>
+      <c r="AF17" s="8"/>
+      <c r="AG17" s="8"/>
+      <c r="AH17" s="9" t="s">
+        <v>3119</v>
+      </c>
+      <c r="AI17" s="9"/>
+      <c r="AJ17" s="9"/>
+      <c r="AK17" s="7"/>
+      <c r="AN17" s="8"/>
+      <c r="AO17" s="8"/>
+    </row>
+    <row r="18" spans="1:41" ht="14.25" customHeight="1">
+      <c r="A18" s="6"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="6"/>
+      <c r="Q18" s="8"/>
+      <c r="R18" s="8"/>
+      <c r="S18" s="9"/>
+      <c r="T18" s="9"/>
+      <c r="U18" s="9"/>
+      <c r="V18" s="9"/>
+      <c r="W18" s="9"/>
+      <c r="X18" s="9"/>
+      <c r="Y18" s="9"/>
+      <c r="Z18" s="9"/>
+      <c r="AA18" s="9"/>
+      <c r="AB18" s="9"/>
+      <c r="AC18" s="9"/>
+      <c r="AD18" s="9"/>
+      <c r="AE18" s="8"/>
+      <c r="AF18" s="8"/>
+      <c r="AG18" s="8"/>
+      <c r="AH18" s="9"/>
+      <c r="AI18" s="9"/>
+      <c r="AJ18" s="9"/>
+      <c r="AK18" s="7"/>
+      <c r="AL18" s="5"/>
+      <c r="AM18" s="5"/>
+      <c r="AN18" s="8"/>
+      <c r="AO18" s="8"/>
+    </row>
+    <row r="19" spans="1:41">
+      <c r="A19" s="6"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="8"/>
+      <c r="Q19" s="8"/>
+      <c r="R19" s="8"/>
+      <c r="S19" s="8" t="s">
+        <v>3108</v>
+      </c>
+      <c r="T19" s="8"/>
+      <c r="U19" s="8"/>
+      <c r="V19" s="8" t="s">
+        <v>3109</v>
+      </c>
+      <c r="W19" s="8"/>
+      <c r="X19" s="8"/>
+      <c r="Y19" s="8" t="s">
+        <v>3110</v>
+      </c>
+      <c r="Z19" s="8"/>
+      <c r="AA19" s="8"/>
+      <c r="AB19" s="8" t="s">
+        <v>3111</v>
+      </c>
+      <c r="AC19" s="8"/>
+      <c r="AD19" s="8"/>
+      <c r="AE19" s="8" t="s">
+        <v>3112</v>
+      </c>
+      <c r="AF19" s="8"/>
+      <c r="AG19" s="8"/>
+      <c r="AH19" s="8" t="s">
+        <v>3113</v>
+      </c>
+      <c r="AI19" s="8"/>
+      <c r="AJ19" s="8"/>
+      <c r="AK19" s="6"/>
+      <c r="AL19" s="5"/>
+      <c r="AM19" s="5"/>
+      <c r="AN19" s="8"/>
+      <c r="AO19" s="8"/>
+    </row>
+    <row r="20" spans="1:41">
+      <c r="A20" s="5"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
+      <c r="R20" s="5"/>
+      <c r="S20" s="8"/>
+      <c r="T20" s="8"/>
+      <c r="U20" s="8"/>
+      <c r="V20" s="8"/>
+      <c r="W20" s="8"/>
+      <c r="X20" s="8"/>
+      <c r="Y20" s="8"/>
+      <c r="Z20" s="8"/>
+      <c r="AA20" s="8"/>
+      <c r="AB20" s="8"/>
+      <c r="AC20" s="8"/>
+      <c r="AD20" s="8"/>
+      <c r="AE20" s="8"/>
+      <c r="AF20" s="8"/>
+      <c r="AG20" s="8"/>
+      <c r="AH20" s="8"/>
+      <c r="AI20" s="8"/>
+      <c r="AJ20" s="8"/>
+      <c r="AK20" s="6"/>
+      <c r="AL20" s="5"/>
+      <c r="AM20" s="5"/>
+      <c r="AN20" s="8"/>
+      <c r="AO20" s="8"/>
+    </row>
+    <row r="21" spans="1:41">
+      <c r="A21" s="6"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="6"/>
+      <c r="J21" s="6"/>
+      <c r="K21" s="6"/>
+      <c r="R21" s="6"/>
+      <c r="S21" s="5"/>
+      <c r="T21" s="5"/>
+      <c r="U21" s="5"/>
+      <c r="V21" s="5"/>
+      <c r="W21" s="5"/>
+      <c r="X21" s="5"/>
+      <c r="Y21" s="5"/>
+      <c r="Z21" s="5"/>
+      <c r="AA21" s="5"/>
+      <c r="AB21" s="5"/>
+      <c r="AC21" s="5"/>
+      <c r="AD21" s="5"/>
+      <c r="AE21" s="5"/>
+      <c r="AF21" s="5"/>
+      <c r="AG21" s="5"/>
+      <c r="AH21" s="5"/>
+      <c r="AI21" s="5"/>
+      <c r="AJ21" s="5"/>
+      <c r="AK21" s="6"/>
+      <c r="AL21" s="5"/>
+      <c r="AM21" s="5"/>
+      <c r="AN21" s="8" t="s">
+        <v>3024</v>
+      </c>
+      <c r="AO21" s="8"/>
+    </row>
+    <row r="22" spans="1:41">
+      <c r="A22" s="5"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="5"/>
+      <c r="R22" s="5"/>
+      <c r="S22" s="9" t="s">
+        <v>3098</v>
+      </c>
+      <c r="T22" s="9"/>
+      <c r="U22" s="9"/>
+      <c r="V22" s="9" t="s">
+        <v>3099</v>
+      </c>
+      <c r="W22" s="9"/>
+      <c r="X22" s="9"/>
+      <c r="Y22" s="9" t="s">
+        <v>3100</v>
+      </c>
+      <c r="Z22" s="9"/>
+      <c r="AA22" s="9"/>
+      <c r="AB22" s="9" t="s">
+        <v>3101</v>
+      </c>
+      <c r="AC22" s="9"/>
+      <c r="AD22" s="9"/>
+      <c r="AE22" s="9" t="s">
+        <v>3102</v>
+      </c>
+      <c r="AF22" s="9"/>
+      <c r="AG22" s="9"/>
+      <c r="AH22" s="9" t="s">
+        <v>3103</v>
+      </c>
+      <c r="AI22" s="9"/>
+      <c r="AJ22" s="9"/>
+      <c r="AK22" s="7"/>
+      <c r="AN22" s="8"/>
+      <c r="AO22" s="8"/>
+    </row>
+    <row r="23" spans="1:41" ht="14.25" customHeight="1">
+      <c r="R23" s="5"/>
+      <c r="S23" s="9"/>
+      <c r="T23" s="9"/>
+      <c r="U23" s="9"/>
+      <c r="V23" s="9"/>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9"/>
+      <c r="Y23" s="9"/>
+      <c r="Z23" s="9"/>
+      <c r="AA23" s="9"/>
+      <c r="AB23" s="9"/>
+      <c r="AC23" s="9"/>
+      <c r="AD23" s="9"/>
+      <c r="AE23" s="9"/>
+      <c r="AF23" s="9"/>
+      <c r="AG23" s="9"/>
+      <c r="AH23" s="9"/>
+      <c r="AI23" s="9"/>
+      <c r="AJ23" s="9"/>
+      <c r="AK23" s="7"/>
+      <c r="AL23" s="5"/>
+      <c r="AM23" s="5"/>
+      <c r="AN23" s="8"/>
+      <c r="AO23" s="8"/>
+    </row>
+    <row r="24" spans="1:41">
+      <c r="A24" s="8" t="s">
+        <v>3087</v>
+      </c>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8" t="s">
+        <v>3088</v>
+      </c>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8" t="s">
+        <v>3089</v>
+      </c>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8" t="s">
+        <v>3090</v>
+      </c>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="8" t="s">
+        <v>3091</v>
+      </c>
+      <c r="N24" s="8"/>
+      <c r="O24" s="8"/>
+      <c r="P24" s="5"/>
+      <c r="Q24" s="5"/>
+      <c r="R24" s="5"/>
+      <c r="S24" s="8" t="s">
+        <v>3092</v>
+      </c>
+      <c r="T24" s="8"/>
+      <c r="U24" s="8"/>
+      <c r="V24" s="8" t="s">
+        <v>3093</v>
+      </c>
+      <c r="W24" s="8"/>
+      <c r="X24" s="8"/>
+      <c r="Y24" s="8" t="s">
+        <v>3094</v>
+      </c>
+      <c r="Z24" s="8"/>
+      <c r="AA24" s="8"/>
+      <c r="AB24" s="8" t="s">
+        <v>3095</v>
+      </c>
+      <c r="AC24" s="8"/>
+      <c r="AD24" s="8"/>
+      <c r="AE24" s="8" t="s">
+        <v>3096</v>
+      </c>
+      <c r="AF24" s="8"/>
+      <c r="AG24" s="8"/>
+      <c r="AH24" s="8" t="s">
+        <v>3097</v>
+      </c>
+      <c r="AI24" s="8"/>
+      <c r="AJ24" s="8"/>
+      <c r="AK24" s="6"/>
+      <c r="AL24" s="5"/>
+      <c r="AM24" s="5"/>
+      <c r="AN24" s="8" t="s">
+        <v>3025</v>
+      </c>
+      <c r="AO24" s="8"/>
+    </row>
+    <row r="25" spans="1:41">
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="8"/>
+      <c r="K25" s="8"/>
+      <c r="L25" s="8"/>
+      <c r="M25" s="8"/>
+      <c r="N25" s="8"/>
+      <c r="O25" s="8"/>
+      <c r="P25" s="5"/>
+      <c r="Q25" s="5"/>
+      <c r="R25" s="5"/>
+      <c r="S25" s="8"/>
+      <c r="T25" s="8"/>
+      <c r="U25" s="8"/>
+      <c r="V25" s="8"/>
+      <c r="W25" s="8"/>
+      <c r="X25" s="8"/>
+      <c r="Y25" s="8"/>
+      <c r="Z25" s="8"/>
+      <c r="AA25" s="8"/>
+      <c r="AB25" s="8"/>
+      <c r="AC25" s="8"/>
+      <c r="AD25" s="8"/>
+      <c r="AE25" s="8"/>
+      <c r="AF25" s="8"/>
+      <c r="AG25" s="8"/>
+      <c r="AH25" s="8"/>
+      <c r="AI25" s="8"/>
+      <c r="AJ25" s="8"/>
+      <c r="AK25" s="6"/>
+      <c r="AL25" s="5"/>
+      <c r="AM25" s="5"/>
+      <c r="AN25" s="8"/>
+      <c r="AO25" s="8"/>
+    </row>
+    <row r="26" spans="1:41">
+      <c r="A26" s="6"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="6"/>
+      <c r="I26" s="6"/>
+      <c r="J26" s="6"/>
+      <c r="K26" s="6"/>
+      <c r="L26" s="6"/>
+      <c r="M26" s="6"/>
+      <c r="N26" s="6"/>
+      <c r="O26" s="6"/>
+      <c r="P26" s="6"/>
+      <c r="Q26" s="6"/>
+      <c r="R26" s="6"/>
+      <c r="S26" s="6"/>
+      <c r="T26" s="6"/>
+      <c r="U26" s="6"/>
+      <c r="V26" s="6"/>
+      <c r="W26" s="6"/>
+      <c r="X26" s="6"/>
+      <c r="Y26" s="6"/>
+      <c r="Z26" s="6"/>
+      <c r="AA26" s="6"/>
+      <c r="AB26" s="6"/>
+      <c r="AC26" s="6"/>
+      <c r="AD26" s="6"/>
+      <c r="AE26" s="6"/>
+      <c r="AF26" s="6"/>
+      <c r="AG26" s="6"/>
+      <c r="AH26" s="6"/>
+      <c r="AI26" s="6"/>
+      <c r="AJ26" s="6"/>
+      <c r="AK26" s="6"/>
+      <c r="AN26" s="8"/>
+      <c r="AO26" s="8"/>
+    </row>
+    <row r="27" spans="1:41">
+      <c r="A27" s="9" t="s">
+        <v>3076</v>
+      </c>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9" t="s">
+        <v>3077</v>
+      </c>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9" t="s">
+        <v>3078</v>
+      </c>
+      <c r="H27" s="9"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="9" t="s">
+        <v>3079</v>
+      </c>
+      <c r="K27" s="9"/>
+      <c r="L27" s="9"/>
+      <c r="M27" s="9" t="s">
+        <v>3080</v>
+      </c>
+      <c r="N27" s="9"/>
+      <c r="O27" s="9"/>
+      <c r="S27" s="9" t="s">
+        <v>3081</v>
+      </c>
+      <c r="T27" s="9"/>
+      <c r="U27" s="9"/>
+      <c r="V27" s="9" t="s">
+        <v>3082</v>
+      </c>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
+      <c r="Y27" s="9" t="s">
+        <v>3083</v>
+      </c>
+      <c r="Z27" s="9"/>
+      <c r="AA27" s="9"/>
+      <c r="AB27" s="9" t="s">
+        <v>3084</v>
+      </c>
+      <c r="AC27" s="9"/>
+      <c r="AD27" s="9"/>
+      <c r="AE27" s="9" t="s">
+        <v>3085</v>
+      </c>
+      <c r="AF27" s="9"/>
+      <c r="AG27" s="9"/>
+      <c r="AH27" s="9" t="s">
+        <v>3086</v>
+      </c>
+      <c r="AI27" s="9"/>
+      <c r="AJ27" s="9"/>
+      <c r="AK27" s="7"/>
+      <c r="AL27" s="5"/>
+      <c r="AM27" s="5"/>
+      <c r="AN27" s="8" t="s">
+        <v>3026</v>
+      </c>
+      <c r="AO27" s="8"/>
+    </row>
+    <row r="28" spans="1:41" ht="14.25" customHeight="1">
+      <c r="A28" s="9"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
+      <c r="J28" s="9"/>
+      <c r="K28" s="9"/>
+      <c r="L28" s="9"/>
+      <c r="M28" s="9"/>
+      <c r="N28" s="9"/>
+      <c r="O28" s="9"/>
+      <c r="P28" s="5"/>
+      <c r="Q28" s="5"/>
+      <c r="R28" s="5"/>
+      <c r="S28" s="9"/>
+      <c r="T28" s="9"/>
+      <c r="U28" s="9"/>
+      <c r="V28" s="9"/>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="9"/>
+      <c r="Z28" s="9"/>
+      <c r="AA28" s="9"/>
+      <c r="AB28" s="9"/>
+      <c r="AC28" s="9"/>
+      <c r="AD28" s="9"/>
+      <c r="AE28" s="9"/>
+      <c r="AF28" s="9"/>
+      <c r="AG28" s="9"/>
+      <c r="AH28" s="9"/>
+      <c r="AI28" s="9"/>
+      <c r="AJ28" s="9"/>
+      <c r="AK28" s="7"/>
+      <c r="AL28" s="5"/>
+      <c r="AM28" s="5"/>
+      <c r="AN28" s="8"/>
+      <c r="AO28" s="8"/>
+    </row>
+    <row r="29" spans="1:41">
+      <c r="A29" s="8" t="s">
+        <v>3065</v>
+      </c>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8" t="s">
+        <v>3066</v>
+      </c>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8" t="s">
+        <v>3067</v>
+      </c>
+      <c r="H29" s="8"/>
+      <c r="I29" s="8"/>
+      <c r="J29" s="8" t="s">
+        <v>3068</v>
+      </c>
+      <c r="K29" s="8"/>
+      <c r="L29" s="8"/>
+      <c r="M29" s="8" t="s">
+        <v>3069</v>
+      </c>
+      <c r="N29" s="8"/>
+      <c r="O29" s="8"/>
+      <c r="P29" s="5"/>
+      <c r="Q29" s="5"/>
+      <c r="R29" s="5"/>
+      <c r="S29" s="8" t="s">
+        <v>3070</v>
+      </c>
+      <c r="T29" s="8"/>
+      <c r="U29" s="8"/>
+      <c r="V29" s="8" t="s">
+        <v>3071</v>
+      </c>
+      <c r="W29" s="8"/>
+      <c r="X29" s="8"/>
+      <c r="Y29" s="8" t="s">
+        <v>3072</v>
+      </c>
+      <c r="Z29" s="8"/>
+      <c r="AA29" s="8"/>
+      <c r="AB29" s="8" t="s">
+        <v>3073</v>
+      </c>
+      <c r="AC29" s="8"/>
+      <c r="AD29" s="8"/>
+      <c r="AE29" s="8" t="s">
+        <v>3074</v>
+      </c>
+      <c r="AF29" s="8"/>
+      <c r="AG29" s="8"/>
+      <c r="AH29" s="8" t="s">
+        <v>3075</v>
+      </c>
+      <c r="AI29" s="8"/>
+      <c r="AJ29" s="8"/>
+      <c r="AK29" s="6"/>
+      <c r="AL29" s="5"/>
+      <c r="AM29" s="5"/>
+      <c r="AN29" s="8"/>
+      <c r="AO29" s="8"/>
+    </row>
+    <row r="30" spans="1:41">
+      <c r="A30" s="8"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="8"/>
+      <c r="J30" s="8"/>
+      <c r="K30" s="8"/>
+      <c r="L30" s="8"/>
+      <c r="M30" s="8"/>
+      <c r="N30" s="8"/>
+      <c r="O30" s="8"/>
+      <c r="P30" s="5"/>
+      <c r="Q30" s="5"/>
+      <c r="R30" s="5"/>
+      <c r="S30" s="8"/>
+      <c r="T30" s="8"/>
+      <c r="U30" s="8"/>
+      <c r="V30" s="8"/>
+      <c r="W30" s="8"/>
+      <c r="X30" s="8"/>
+      <c r="Y30" s="8"/>
+      <c r="Z30" s="8"/>
+      <c r="AA30" s="8"/>
+      <c r="AB30" s="8"/>
+      <c r="AC30" s="8"/>
+      <c r="AD30" s="8"/>
+      <c r="AE30" s="8"/>
+      <c r="AF30" s="8"/>
+      <c r="AG30" s="8"/>
+      <c r="AH30" s="8"/>
+      <c r="AI30" s="8"/>
+      <c r="AJ30" s="8"/>
+      <c r="AK30" s="6"/>
+      <c r="AN30" s="8" t="s">
+        <v>3027</v>
+      </c>
+      <c r="AO30" s="8"/>
+    </row>
+    <row r="31" spans="1:41">
+      <c r="A31" s="6"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="6"/>
+      <c r="I31" s="6"/>
+      <c r="J31" s="6"/>
+      <c r="K31" s="6"/>
+      <c r="L31" s="6"/>
+      <c r="M31" s="6"/>
+      <c r="N31" s="6"/>
+      <c r="O31" s="6"/>
+      <c r="P31" s="6"/>
+      <c r="Q31" s="6"/>
+      <c r="R31" s="6"/>
+      <c r="S31" s="6"/>
+      <c r="T31" s="6"/>
+      <c r="U31" s="6"/>
+      <c r="V31" s="6"/>
+      <c r="W31" s="6"/>
+      <c r="X31" s="6"/>
+      <c r="Y31" s="6"/>
+      <c r="Z31" s="6"/>
+      <c r="AA31" s="6"/>
+      <c r="AB31" s="6"/>
+      <c r="AC31" s="6"/>
+      <c r="AD31" s="6"/>
+      <c r="AE31" s="6"/>
+      <c r="AF31" s="6"/>
+      <c r="AG31" s="6"/>
+      <c r="AH31" s="6"/>
+      <c r="AI31" s="6"/>
+      <c r="AJ31" s="6"/>
+      <c r="AK31" s="6"/>
+      <c r="AN31" s="8"/>
+      <c r="AO31" s="8"/>
+    </row>
+    <row r="32" spans="1:41">
+      <c r="A32" s="9" t="s">
+        <v>3054</v>
+      </c>
+      <c r="B32" s="9"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9" t="s">
+        <v>3055</v>
+      </c>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="9" t="s">
+        <v>3056</v>
+      </c>
+      <c r="H32" s="9"/>
+      <c r="I32" s="9"/>
+      <c r="J32" s="9" t="s">
+        <v>3057</v>
+      </c>
+      <c r="K32" s="9"/>
+      <c r="L32" s="9"/>
+      <c r="M32" s="9" t="s">
+        <v>3058</v>
+      </c>
+      <c r="N32" s="9"/>
+      <c r="O32" s="9"/>
+      <c r="S32" s="9" t="s">
+        <v>3059</v>
+      </c>
+      <c r="T32" s="9"/>
+      <c r="U32" s="9"/>
+      <c r="V32" s="9" t="s">
+        <v>3060</v>
+      </c>
+      <c r="W32" s="9"/>
+      <c r="X32" s="9"/>
+      <c r="Y32" s="9" t="s">
+        <v>3061</v>
+      </c>
+      <c r="Z32" s="9"/>
+      <c r="AA32" s="9"/>
+      <c r="AB32" s="9" t="s">
+        <v>3062</v>
+      </c>
+      <c r="AC32" s="9"/>
+      <c r="AD32" s="9"/>
+      <c r="AE32" s="9" t="s">
+        <v>3063</v>
+      </c>
+      <c r="AF32" s="9"/>
+      <c r="AG32" s="9"/>
+      <c r="AH32" s="9" t="s">
+        <v>3064</v>
+      </c>
+      <c r="AI32" s="9"/>
+      <c r="AJ32" s="9"/>
+      <c r="AK32" s="7"/>
+      <c r="AL32" s="5"/>
+      <c r="AM32" s="5"/>
+      <c r="AN32" s="8"/>
+      <c r="AO32" s="8"/>
+    </row>
+    <row r="33" spans="1:41" ht="14.25" customHeight="1">
+      <c r="A33" s="9"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="9"/>
+      <c r="H33" s="9"/>
+      <c r="I33" s="9"/>
+      <c r="J33" s="9"/>
+      <c r="K33" s="9"/>
+      <c r="L33" s="9"/>
+      <c r="M33" s="9"/>
+      <c r="N33" s="9"/>
+      <c r="O33" s="9"/>
+      <c r="P33" s="8"/>
+      <c r="Q33" s="8"/>
+      <c r="R33" s="8"/>
+      <c r="S33" s="9"/>
+      <c r="T33" s="9"/>
+      <c r="U33" s="9"/>
+      <c r="V33" s="9"/>
+      <c r="W33" s="9"/>
+      <c r="X33" s="9"/>
+      <c r="Y33" s="9"/>
+      <c r="Z33" s="9"/>
+      <c r="AA33" s="9"/>
+      <c r="AB33" s="9"/>
+      <c r="AC33" s="9"/>
+      <c r="AD33" s="9"/>
+      <c r="AE33" s="9"/>
+      <c r="AF33" s="9"/>
+      <c r="AG33" s="9"/>
+      <c r="AH33" s="9"/>
+      <c r="AI33" s="9"/>
+      <c r="AJ33" s="9"/>
+      <c r="AK33" s="7"/>
+      <c r="AL33" s="5"/>
+      <c r="AM33" s="5"/>
+      <c r="AN33" s="8" t="s">
+        <v>3028</v>
+      </c>
+      <c r="AO33" s="8"/>
+    </row>
+    <row r="34" spans="1:41">
+      <c r="A34" s="8" t="s">
+        <v>3043</v>
+      </c>
+      <c r="B34" s="8"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="8" t="s">
+        <v>3044</v>
+      </c>
+      <c r="E34" s="8"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="8" t="s">
+        <v>3045</v>
+      </c>
+      <c r="H34" s="8"/>
+      <c r="I34" s="8"/>
+      <c r="J34" s="8" t="s">
+        <v>3046</v>
+      </c>
+      <c r="K34" s="8"/>
+      <c r="L34" s="8"/>
+      <c r="M34" s="8" t="s">
+        <v>3047</v>
+      </c>
+      <c r="N34" s="8"/>
+      <c r="O34" s="8"/>
+      <c r="P34" s="8"/>
+      <c r="Q34" s="8"/>
+      <c r="R34" s="8"/>
+      <c r="S34" s="8" t="s">
+        <v>3048</v>
+      </c>
+      <c r="T34" s="8"/>
+      <c r="U34" s="8"/>
+      <c r="V34" s="8" t="s">
+        <v>3049</v>
+      </c>
+      <c r="W34" s="8"/>
+      <c r="X34" s="8"/>
+      <c r="Y34" s="8" t="s">
+        <v>3050</v>
+      </c>
+      <c r="Z34" s="8"/>
+      <c r="AA34" s="8"/>
+      <c r="AB34" s="8" t="s">
+        <v>3051</v>
+      </c>
+      <c r="AC34" s="8"/>
+      <c r="AD34" s="8"/>
+      <c r="AE34" s="8" t="s">
+        <v>3052</v>
+      </c>
+      <c r="AF34" s="8"/>
+      <c r="AG34" s="8"/>
+      <c r="AH34" s="8" t="s">
+        <v>3053</v>
+      </c>
+      <c r="AI34" s="8"/>
+      <c r="AJ34" s="8"/>
+      <c r="AK34" s="6"/>
+      <c r="AL34" s="5"/>
+      <c r="AM34" s="5"/>
+      <c r="AN34" s="8"/>
+      <c r="AO34" s="8"/>
+    </row>
+    <row r="35" spans="1:41">
+      <c r="A35" s="8"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="8"/>
+      <c r="I35" s="8"/>
+      <c r="J35" s="8"/>
+      <c r="K35" s="8"/>
+      <c r="L35" s="8"/>
+      <c r="M35" s="8"/>
+      <c r="N35" s="8"/>
+      <c r="O35" s="8"/>
+      <c r="P35" s="5"/>
+      <c r="Q35" s="5"/>
+      <c r="R35" s="5"/>
+      <c r="S35" s="8"/>
+      <c r="T35" s="8"/>
+      <c r="U35" s="8"/>
+      <c r="V35" s="8"/>
+      <c r="W35" s="8"/>
+      <c r="X35" s="8"/>
+      <c r="Y35" s="8"/>
+      <c r="Z35" s="8"/>
+      <c r="AA35" s="8"/>
+      <c r="AB35" s="8"/>
+      <c r="AC35" s="8"/>
+      <c r="AD35" s="8"/>
+      <c r="AE35" s="8"/>
+      <c r="AF35" s="8"/>
+      <c r="AG35" s="8"/>
+      <c r="AH35" s="8"/>
+      <c r="AI35" s="8"/>
+      <c r="AJ35" s="8"/>
+      <c r="AK35" s="6"/>
+      <c r="AN35" s="8"/>
+      <c r="AO35" s="8"/>
+    </row>
+    <row r="36" spans="1:41">
+      <c r="A36" s="6"/>
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
+      <c r="H36" s="6"/>
+      <c r="I36" s="6"/>
+      <c r="J36" s="6"/>
+      <c r="K36" s="6"/>
+      <c r="L36" s="6"/>
+      <c r="M36" s="6"/>
+      <c r="N36" s="6"/>
+      <c r="O36" s="6"/>
+      <c r="P36" s="6"/>
+      <c r="Q36" s="6"/>
+      <c r="R36" s="6"/>
+      <c r="S36" s="6"/>
+      <c r="T36" s="6"/>
+      <c r="U36" s="6"/>
+      <c r="V36" s="6"/>
+      <c r="W36" s="6"/>
+      <c r="X36" s="6"/>
+      <c r="Y36" s="6"/>
+      <c r="Z36" s="6"/>
+      <c r="AA36" s="6"/>
+      <c r="AB36" s="6"/>
+      <c r="AC36" s="6"/>
+      <c r="AD36" s="6"/>
+      <c r="AE36" s="6"/>
+      <c r="AF36" s="6"/>
+      <c r="AG36" s="6"/>
+      <c r="AH36" s="6"/>
+      <c r="AI36" s="6"/>
+      <c r="AJ36" s="6"/>
+      <c r="AK36" s="6"/>
+      <c r="AN36" s="8" t="s">
+        <v>3029</v>
+      </c>
+      <c r="AO36" s="8"/>
+    </row>
+    <row r="37" spans="1:41">
+      <c r="A37" s="9" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9" t="s">
+        <v>3033</v>
+      </c>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="9" t="s">
+        <v>3034</v>
+      </c>
+      <c r="H37" s="9"/>
+      <c r="I37" s="9"/>
+      <c r="J37" s="9" t="s">
+        <v>3035</v>
+      </c>
+      <c r="K37" s="9"/>
+      <c r="L37" s="9"/>
+      <c r="M37" s="9" t="s">
+        <v>3036</v>
+      </c>
+      <c r="N37" s="9"/>
+      <c r="O37" s="9"/>
+      <c r="S37" s="9" t="s">
+        <v>3037</v>
+      </c>
+      <c r="T37" s="9"/>
+      <c r="U37" s="9"/>
+      <c r="V37" s="9" t="s">
+        <v>3038</v>
+      </c>
+      <c r="W37" s="9"/>
+      <c r="X37" s="9"/>
+      <c r="Y37" s="9" t="s">
+        <v>3039</v>
+      </c>
+      <c r="Z37" s="9"/>
+      <c r="AA37" s="9"/>
+      <c r="AB37" s="9" t="s">
+        <v>3040</v>
+      </c>
+      <c r="AC37" s="9"/>
+      <c r="AD37" s="9"/>
+      <c r="AE37" s="9" t="s">
+        <v>3041</v>
+      </c>
+      <c r="AF37" s="9"/>
+      <c r="AG37" s="9"/>
+      <c r="AH37" s="9" t="s">
+        <v>3042</v>
+      </c>
+      <c r="AI37" s="9"/>
+      <c r="AJ37" s="9"/>
+      <c r="AK37" s="7"/>
+      <c r="AL37" s="5"/>
+      <c r="AM37" s="5"/>
+      <c r="AN37" s="8"/>
+      <c r="AO37" s="8"/>
+    </row>
+    <row r="38" spans="1:41" ht="14.25" customHeight="1">
+      <c r="A38" s="9"/>
+      <c r="B38" s="9"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="9"/>
+      <c r="F38" s="9"/>
+      <c r="G38" s="9"/>
+      <c r="H38" s="9"/>
+      <c r="I38" s="9"/>
+      <c r="J38" s="9"/>
+      <c r="K38" s="9"/>
+      <c r="L38" s="9"/>
+      <c r="M38" s="9"/>
+      <c r="N38" s="9"/>
+      <c r="O38" s="9"/>
+      <c r="P38" s="8"/>
+      <c r="Q38" s="8"/>
+      <c r="R38" s="8"/>
+      <c r="S38" s="9"/>
+      <c r="T38" s="9"/>
+      <c r="U38" s="9"/>
+      <c r="V38" s="9"/>
+      <c r="W38" s="9"/>
+      <c r="X38" s="9"/>
+      <c r="Y38" s="9"/>
+      <c r="Z38" s="9"/>
+      <c r="AA38" s="9"/>
+      <c r="AB38" s="9"/>
+      <c r="AC38" s="9"/>
+      <c r="AD38" s="9"/>
+      <c r="AE38" s="9"/>
+      <c r="AF38" s="9"/>
+      <c r="AG38" s="9"/>
+      <c r="AH38" s="9"/>
+      <c r="AI38" s="9"/>
+      <c r="AJ38" s="9"/>
+      <c r="AK38" s="7"/>
+      <c r="AL38" s="5"/>
+      <c r="AM38" s="5"/>
+      <c r="AN38" s="8"/>
+      <c r="AO38" s="8"/>
+    </row>
+    <row r="39" spans="1:41">
+      <c r="A39" s="8" t="s">
+        <v>3007</v>
+      </c>
+      <c r="B39" s="8"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="8" t="s">
+        <v>3008</v>
+      </c>
+      <c r="E39" s="8"/>
+      <c r="F39" s="8"/>
+      <c r="G39" s="8" t="s">
+        <v>3009</v>
+      </c>
+      <c r="H39" s="8"/>
+      <c r="I39" s="8"/>
+      <c r="J39" s="8" t="s">
+        <v>3010</v>
+      </c>
+      <c r="K39" s="8"/>
+      <c r="L39" s="8"/>
+      <c r="M39" s="8" t="s">
+        <v>3011</v>
+      </c>
+      <c r="N39" s="8"/>
+      <c r="O39" s="8"/>
+      <c r="P39" s="8"/>
+      <c r="Q39" s="8"/>
+      <c r="R39" s="8"/>
+      <c r="S39" s="8" t="s">
+        <v>3012</v>
+      </c>
+      <c r="T39" s="8"/>
+      <c r="U39" s="8"/>
+      <c r="V39" s="8" t="s">
+        <v>3013</v>
+      </c>
+      <c r="W39" s="8"/>
+      <c r="X39" s="8"/>
+      <c r="Y39" s="8" t="s">
+        <v>3014</v>
+      </c>
+      <c r="Z39" s="8"/>
+      <c r="AA39" s="8"/>
+      <c r="AB39" s="8" t="s">
+        <v>3015</v>
+      </c>
+      <c r="AC39" s="8"/>
+      <c r="AD39" s="8"/>
+      <c r="AE39" s="8" t="s">
+        <v>3016</v>
+      </c>
+      <c r="AF39" s="8"/>
+      <c r="AG39" s="8"/>
+      <c r="AH39" s="8" t="s">
+        <v>3017</v>
+      </c>
+      <c r="AI39" s="8"/>
+      <c r="AJ39" s="8"/>
+      <c r="AK39" s="6"/>
+      <c r="AL39" s="5"/>
+      <c r="AM39" s="5"/>
+      <c r="AN39" s="8" t="s">
+        <v>3030</v>
+      </c>
+      <c r="AO39" s="8"/>
+    </row>
+    <row r="40" spans="1:41">
+      <c r="A40" s="8"/>
+      <c r="B40" s="8"/>
+      <c r="C40" s="8"/>
+      <c r="D40" s="8"/>
+      <c r="E40" s="8"/>
+      <c r="F40" s="8"/>
+      <c r="G40" s="8"/>
+      <c r="H40" s="8"/>
+      <c r="I40" s="8"/>
+      <c r="J40" s="8"/>
+      <c r="K40" s="8"/>
+      <c r="L40" s="8"/>
+      <c r="M40" s="8"/>
+      <c r="N40" s="8"/>
+      <c r="O40" s="8"/>
+      <c r="P40" s="8"/>
+      <c r="Q40" s="8"/>
+      <c r="R40" s="8"/>
+      <c r="S40" s="8"/>
+      <c r="T40" s="8"/>
+      <c r="U40" s="8"/>
+      <c r="V40" s="8"/>
+      <c r="W40" s="8"/>
+      <c r="X40" s="8"/>
+      <c r="Y40" s="8"/>
+      <c r="Z40" s="8"/>
+      <c r="AA40" s="8"/>
+      <c r="AB40" s="8"/>
+      <c r="AC40" s="8"/>
+      <c r="AD40" s="8"/>
+      <c r="AE40" s="8"/>
+      <c r="AF40" s="8"/>
+      <c r="AG40" s="8"/>
+      <c r="AH40" s="8"/>
+      <c r="AI40" s="8"/>
+      <c r="AJ40" s="8"/>
+      <c r="AK40" s="6"/>
+      <c r="AL40" s="5"/>
+      <c r="AM40" s="5"/>
+      <c r="AN40" s="8"/>
+      <c r="AO40" s="8"/>
+    </row>
+    <row r="41" spans="1:41">
+      <c r="A41" s="6"/>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="6"/>
+      <c r="H41" s="6"/>
+      <c r="I41" s="6"/>
+      <c r="J41" s="6"/>
+      <c r="K41" s="6"/>
+      <c r="L41" s="6"/>
+      <c r="M41" s="6"/>
+      <c r="N41" s="6"/>
+      <c r="O41" s="6"/>
+      <c r="P41" s="6"/>
+      <c r="Q41" s="6"/>
+      <c r="R41" s="6"/>
+      <c r="S41" s="6"/>
+      <c r="T41" s="6"/>
+      <c r="U41" s="6"/>
+      <c r="V41" s="6"/>
+      <c r="W41" s="6"/>
+      <c r="X41" s="6"/>
+      <c r="Y41" s="6"/>
+      <c r="Z41" s="6"/>
+      <c r="AA41" s="6"/>
+      <c r="AB41" s="6"/>
+      <c r="AC41" s="6"/>
+      <c r="AD41" s="6"/>
+      <c r="AE41" s="6"/>
+      <c r="AF41" s="6"/>
+      <c r="AG41" s="6"/>
+      <c r="AH41" s="6"/>
+      <c r="AI41" s="6"/>
+      <c r="AJ41" s="6"/>
+      <c r="AK41" s="6"/>
+      <c r="AL41" s="6"/>
+      <c r="AM41" s="6"/>
+      <c r="AN41" s="8"/>
+      <c r="AO41" s="8"/>
+    </row>
+    <row r="42" spans="1:41">
+      <c r="A42" s="6"/>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="6"/>
+      <c r="H42" s="6"/>
+      <c r="I42" s="6"/>
+      <c r="J42" s="6"/>
+      <c r="K42" s="6"/>
+      <c r="L42" s="6"/>
+      <c r="M42" s="6"/>
+      <c r="N42" s="6"/>
+      <c r="O42" s="6"/>
+      <c r="P42" s="6"/>
+      <c r="Q42" s="6"/>
+      <c r="R42" s="6"/>
+      <c r="S42" s="6"/>
+      <c r="T42" s="6"/>
+      <c r="U42" s="6"/>
+      <c r="V42" s="6"/>
+      <c r="W42" s="6"/>
+      <c r="X42" s="6"/>
+      <c r="Y42" s="6"/>
+      <c r="Z42" s="6"/>
+      <c r="AA42" s="6"/>
+      <c r="AB42" s="6"/>
+      <c r="AC42" s="6"/>
+      <c r="AD42" s="6"/>
+      <c r="AE42" s="6"/>
+      <c r="AF42" s="6"/>
+      <c r="AG42" s="6"/>
+      <c r="AH42" s="6"/>
+      <c r="AI42" s="6"/>
+      <c r="AJ42" s="6"/>
+      <c r="AK42" s="6"/>
+      <c r="AL42" s="6"/>
+      <c r="AM42" s="6"/>
+      <c r="AN42" s="8" t="s">
+        <v>3031</v>
+      </c>
+      <c r="AO42" s="8"/>
+    </row>
+    <row r="43" spans="1:41">
+      <c r="A43" s="5"/>
+      <c r="B43" s="5"/>
+      <c r="C43" s="5"/>
+      <c r="D43" s="5"/>
+      <c r="E43" s="5"/>
+      <c r="F43" s="5"/>
+      <c r="G43" s="5"/>
+      <c r="H43" s="5"/>
+      <c r="I43" s="5"/>
+      <c r="J43" s="5"/>
+      <c r="K43" s="5"/>
+      <c r="L43" s="5"/>
+      <c r="M43" s="5"/>
+      <c r="N43" s="5"/>
+      <c r="O43" s="5"/>
+      <c r="P43" s="5"/>
+      <c r="Q43" s="5"/>
+      <c r="R43" s="5"/>
+      <c r="S43" s="5"/>
+      <c r="T43" s="5"/>
+      <c r="U43" s="5"/>
+      <c r="V43" s="5"/>
+      <c r="W43" s="5"/>
+      <c r="X43" s="5"/>
+      <c r="Y43" s="5"/>
+      <c r="Z43" s="5"/>
+      <c r="AA43" s="5"/>
+      <c r="AB43" s="5"/>
+      <c r="AC43" s="5"/>
+      <c r="AD43" s="5"/>
+      <c r="AE43" s="5"/>
+      <c r="AF43" s="5"/>
+      <c r="AG43" s="5"/>
+      <c r="AH43" s="5"/>
+      <c r="AI43" s="5"/>
+      <c r="AJ43" s="5"/>
+      <c r="AK43" s="6"/>
+      <c r="AL43" s="5"/>
+      <c r="AM43" s="5"/>
+      <c r="AN43" s="8"/>
+      <c r="AO43" s="8"/>
+    </row>
+    <row r="44" spans="1:41" ht="14.25" customHeight="1">
+      <c r="A44" s="5"/>
+      <c r="B44" s="5"/>
+      <c r="C44" s="5"/>
+      <c r="D44" s="5"/>
+      <c r="E44" s="5"/>
+      <c r="F44" s="5"/>
+      <c r="G44" s="5"/>
+      <c r="H44" s="5"/>
+      <c r="I44" s="5"/>
+      <c r="J44" s="5"/>
+      <c r="K44" s="5"/>
+      <c r="L44" s="5"/>
+      <c r="M44" s="5"/>
+      <c r="N44" s="5"/>
+      <c r="O44" s="5"/>
+      <c r="P44" s="5"/>
+      <c r="Q44" s="5"/>
+      <c r="R44" s="5"/>
+      <c r="S44" s="5"/>
+      <c r="T44" s="5"/>
+      <c r="U44" s="5"/>
+      <c r="V44" s="5"/>
+      <c r="W44" s="5"/>
+      <c r="X44" s="5"/>
+      <c r="Y44" s="5"/>
+      <c r="Z44" s="9" t="s">
         <v>3146</v>
       </c>
-      <c r="M1" t="s">
-        <v>3147</v>
-      </c>
-      <c r="N1" t="s">
-        <v>3021</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" t="s">
-        <v>3019</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3019</v>
-      </c>
-      <c r="C2" t="s">
-        <v>3019</v>
-      </c>
-      <c r="D2" t="s">
-        <v>3019</v>
-      </c>
-      <c r="E2" t="s">
-        <v>3019</v>
-      </c>
-      <c r="F2" t="s">
-        <v>3019</v>
-      </c>
-      <c r="G2" t="s">
-        <v>3019</v>
-      </c>
-      <c r="H2" t="s">
-        <v>3019</v>
-      </c>
-      <c r="I2" t="s">
-        <v>3019</v>
-      </c>
-      <c r="J2" t="s">
-        <v>3019</v>
-      </c>
-      <c r="K2" t="s">
-        <v>3019</v>
-      </c>
-      <c r="L2" t="s">
-        <v>3019</v>
-      </c>
-      <c r="M2" t="s">
-        <v>3019</v>
-      </c>
-      <c r="N2" t="s">
-        <v>3022</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" t="s">
-        <v>3153</v>
-      </c>
-      <c r="B3" t="s">
-        <v>3153</v>
-      </c>
-      <c r="C3" t="s">
-        <v>3153</v>
-      </c>
-      <c r="D3" t="s">
-        <v>3153</v>
-      </c>
-      <c r="E3" t="s">
-        <v>3019</v>
-      </c>
-      <c r="F3" t="s">
-        <v>3106</v>
-      </c>
-      <c r="G3" t="s">
-        <v>3140</v>
-      </c>
-      <c r="H3" t="s">
-        <v>3141</v>
-      </c>
-      <c r="I3" t="s">
-        <v>3142</v>
-      </c>
-      <c r="J3" t="s">
-        <v>3143</v>
-      </c>
-      <c r="K3" t="s">
-        <v>3144</v>
-      </c>
-      <c r="L3" t="s">
-        <v>3145</v>
-      </c>
-      <c r="M3" t="s">
-        <v>3019</v>
-      </c>
-      <c r="N3" t="s">
-        <v>3023</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" t="s">
-        <v>3153</v>
-      </c>
-      <c r="B4" t="s">
-        <v>3153</v>
-      </c>
-      <c r="C4" t="s">
-        <v>3153</v>
-      </c>
-      <c r="D4" t="s">
-        <v>3153</v>
-      </c>
-      <c r="E4" t="s">
-        <v>3019</v>
-      </c>
-      <c r="F4" t="s">
-        <v>3106</v>
-      </c>
-      <c r="G4" t="s">
-        <v>3134</v>
-      </c>
-      <c r="H4" t="s">
-        <v>3135</v>
-      </c>
-      <c r="I4" t="s">
-        <v>3136</v>
-      </c>
-      <c r="J4" t="s">
-        <v>3137</v>
-      </c>
-      <c r="K4" t="s">
-        <v>3138</v>
-      </c>
-      <c r="L4" t="s">
-        <v>3139</v>
-      </c>
-      <c r="M4" t="s">
-        <v>3019</v>
-      </c>
-      <c r="N4" t="s">
-        <v>3023</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" t="s">
-        <v>3153</v>
-      </c>
-      <c r="B5" t="s">
-        <v>3153</v>
-      </c>
-      <c r="C5" t="s">
-        <v>3153</v>
-      </c>
-      <c r="D5" t="s">
-        <v>3153</v>
-      </c>
-      <c r="E5" t="s">
-        <v>3019</v>
-      </c>
-      <c r="F5" t="s">
-        <v>3107</v>
-      </c>
-      <c r="G5" t="s">
-        <v>3019</v>
-      </c>
-      <c r="H5" t="s">
-        <v>3019</v>
-      </c>
-      <c r="I5" t="s">
-        <v>3019</v>
-      </c>
-      <c r="J5" t="s">
-        <v>3019</v>
-      </c>
-      <c r="K5" t="s">
-        <v>3019</v>
-      </c>
-      <c r="L5" t="s">
-        <v>3019</v>
-      </c>
-      <c r="M5" t="s">
-        <v>3019</v>
-      </c>
-      <c r="N5" t="s">
-        <v>3024</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" t="s">
-        <v>3153</v>
-      </c>
-      <c r="B6" t="s">
-        <v>3153</v>
-      </c>
-      <c r="C6" t="s">
-        <v>3153</v>
-      </c>
-      <c r="D6" t="s">
-        <v>3153</v>
-      </c>
-      <c r="E6" t="s">
-        <v>3019</v>
-      </c>
-      <c r="F6" t="s">
-        <v>3107</v>
-      </c>
-      <c r="G6" t="s">
-        <v>3128</v>
-      </c>
-      <c r="H6" t="s">
-        <v>3129</v>
-      </c>
-      <c r="I6" t="s">
-        <v>3130</v>
-      </c>
-      <c r="J6" t="s">
-        <v>3131</v>
-      </c>
-      <c r="K6" t="s">
-        <v>3132</v>
-      </c>
-      <c r="L6" t="s">
-        <v>3133</v>
-      </c>
-      <c r="M6" t="s">
-        <v>3019</v>
-      </c>
-      <c r="N6" t="s">
-        <v>3024</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" t="s">
-        <v>3153</v>
-      </c>
-      <c r="B7" t="s">
-        <v>3153</v>
-      </c>
-      <c r="C7" t="s">
-        <v>3153</v>
-      </c>
-      <c r="D7" t="s">
-        <v>3153</v>
-      </c>
-      <c r="E7" t="s">
-        <v>3019</v>
-      </c>
-      <c r="F7" t="s">
-        <v>3108</v>
-      </c>
-      <c r="G7" t="s">
-        <v>3122</v>
-      </c>
-      <c r="H7" t="s">
-        <v>3123</v>
-      </c>
-      <c r="I7" t="s">
-        <v>3124</v>
-      </c>
-      <c r="J7" t="s">
-        <v>3125</v>
-      </c>
-      <c r="K7" t="s">
-        <v>3126</v>
-      </c>
-      <c r="L7" t="s">
-        <v>3127</v>
-      </c>
-      <c r="M7" t="s">
-        <v>3019</v>
-      </c>
-      <c r="N7" t="s">
-        <v>3025</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" t="s">
-        <v>3153</v>
-      </c>
-      <c r="B8" t="s">
-        <v>3153</v>
-      </c>
-      <c r="C8" t="s">
-        <v>3153</v>
-      </c>
-      <c r="D8" t="s">
-        <v>3153</v>
-      </c>
-      <c r="E8" t="s">
-        <v>3019</v>
-      </c>
-      <c r="F8" t="s">
-        <v>3108</v>
-      </c>
-      <c r="G8" t="s">
-        <v>3019</v>
-      </c>
-      <c r="H8" t="s">
-        <v>3019</v>
-      </c>
-      <c r="I8" t="s">
-        <v>3019</v>
-      </c>
-      <c r="J8" t="s">
-        <v>3019</v>
-      </c>
-      <c r="K8" t="s">
-        <v>3019</v>
-      </c>
-      <c r="L8" t="s">
-        <v>3019</v>
-      </c>
-      <c r="M8" t="s">
-        <v>3019</v>
-      </c>
-      <c r="N8" t="s">
-        <v>3025</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" t="s">
-        <v>3153</v>
-      </c>
-      <c r="B9" t="s">
-        <v>3153</v>
-      </c>
-      <c r="C9" t="s">
-        <v>3153</v>
-      </c>
-      <c r="D9" t="s">
-        <v>3153</v>
-      </c>
-      <c r="E9" t="s">
-        <v>3019</v>
-      </c>
-      <c r="F9" t="s">
-        <v>3109</v>
-      </c>
-      <c r="G9" t="s">
-        <v>3116</v>
-      </c>
-      <c r="H9" t="s">
-        <v>3117</v>
-      </c>
-      <c r="I9" t="s">
-        <v>3118</v>
-      </c>
-      <c r="J9" t="s">
-        <v>3119</v>
-      </c>
-      <c r="K9" t="s">
-        <v>3120</v>
-      </c>
-      <c r="L9" t="s">
-        <v>3121</v>
-      </c>
-      <c r="M9" t="s">
-        <v>3019</v>
-      </c>
-      <c r="N9" t="s">
-        <v>3019</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" t="s">
-        <v>3153</v>
-      </c>
-      <c r="B10" t="s">
-        <v>3153</v>
-      </c>
-      <c r="C10" t="s">
-        <v>3153</v>
-      </c>
-      <c r="D10" t="s">
-        <v>3153</v>
-      </c>
-      <c r="E10" t="s">
-        <v>3019</v>
-      </c>
-      <c r="F10" t="s">
-        <v>3109</v>
-      </c>
-      <c r="G10" t="s">
-        <v>3110</v>
-      </c>
-      <c r="H10" t="s">
-        <v>3111</v>
-      </c>
-      <c r="I10" t="s">
-        <v>3112</v>
-      </c>
-      <c r="J10" t="s">
-        <v>3113</v>
-      </c>
-      <c r="K10" t="s">
-        <v>3114</v>
-      </c>
-      <c r="L10" t="s">
-        <v>3115</v>
-      </c>
-      <c r="M10" t="s">
-        <v>3019</v>
-      </c>
-      <c r="N10" t="s">
-        <v>3026</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" t="s">
-        <v>3019</v>
-      </c>
-      <c r="B11" t="s">
-        <v>3019</v>
-      </c>
-      <c r="C11" t="s">
-        <v>3019</v>
-      </c>
-      <c r="D11" t="s">
-        <v>3019</v>
-      </c>
-      <c r="E11" t="s">
-        <v>3019</v>
-      </c>
-      <c r="F11" t="s">
-        <v>3019</v>
-      </c>
-      <c r="G11" t="s">
-        <v>3019</v>
-      </c>
-      <c r="H11" t="s">
-        <v>3019</v>
-      </c>
-      <c r="I11" t="s">
-        <v>3019</v>
-      </c>
-      <c r="J11" t="s">
-        <v>3019</v>
-      </c>
-      <c r="K11" t="s">
-        <v>3019</v>
-      </c>
-      <c r="L11" t="s">
-        <v>3019</v>
-      </c>
-      <c r="M11" t="s">
-        <v>3019</v>
-      </c>
-      <c r="N11" t="s">
-        <v>3027</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="F12" t="s">
-        <v>3019</v>
-      </c>
-      <c r="G12" t="s">
-        <v>3100</v>
-      </c>
-      <c r="H12" t="s">
-        <v>3101</v>
-      </c>
-      <c r="I12" t="s">
-        <v>3102</v>
-      </c>
-      <c r="J12" t="s">
-        <v>3103</v>
-      </c>
-      <c r="K12" t="s">
-        <v>3104</v>
-      </c>
-      <c r="L12" t="s">
-        <v>3105</v>
-      </c>
-      <c r="M12" t="s">
-        <v>3019</v>
-      </c>
-      <c r="N12" t="s">
-        <v>3027</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" t="s">
-        <v>3089</v>
-      </c>
-      <c r="B13" t="s">
-        <v>3090</v>
-      </c>
-      <c r="C13" t="s">
-        <v>3091</v>
-      </c>
-      <c r="D13" t="s">
-        <v>3092</v>
-      </c>
-      <c r="E13" t="s">
-        <v>3093</v>
-      </c>
-      <c r="F13" t="s">
-        <v>3019</v>
-      </c>
-      <c r="G13" t="s">
-        <v>3094</v>
-      </c>
-      <c r="H13" t="s">
-        <v>3095</v>
-      </c>
-      <c r="I13" t="s">
-        <v>3096</v>
-      </c>
-      <c r="J13" t="s">
-        <v>3097</v>
-      </c>
-      <c r="K13" t="s">
-        <v>3098</v>
-      </c>
-      <c r="L13" t="s">
-        <v>3099</v>
-      </c>
-      <c r="M13" t="s">
-        <v>3019</v>
-      </c>
-      <c r="N13" t="s">
-        <v>3028</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="A14" t="s">
-        <v>3019</v>
-      </c>
-      <c r="B14" t="s">
-        <v>3019</v>
-      </c>
-      <c r="C14" t="s">
-        <v>3019</v>
-      </c>
-      <c r="D14" t="s">
-        <v>3019</v>
-      </c>
-      <c r="E14" t="s">
-        <v>3019</v>
-      </c>
-      <c r="F14" t="s">
-        <v>3019</v>
-      </c>
-      <c r="G14" t="s">
-        <v>3019</v>
-      </c>
-      <c r="H14" t="s">
-        <v>3019</v>
-      </c>
-      <c r="I14" t="s">
-        <v>3019</v>
-      </c>
-      <c r="J14" t="s">
-        <v>3019</v>
-      </c>
-      <c r="K14" t="s">
-        <v>3019</v>
-      </c>
-      <c r="L14" t="s">
-        <v>3019</v>
-      </c>
-      <c r="M14" t="s">
-        <v>3019</v>
-      </c>
-      <c r="N14" t="s">
-        <v>3028</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="A15" t="s">
-        <v>3078</v>
-      </c>
-      <c r="B15" t="s">
-        <v>3079</v>
-      </c>
-      <c r="C15" t="s">
-        <v>3080</v>
-      </c>
-      <c r="D15" t="s">
-        <v>3081</v>
-      </c>
-      <c r="E15" t="s">
-        <v>3082</v>
-      </c>
-      <c r="F15" t="s">
-        <v>3019</v>
-      </c>
-      <c r="G15" t="s">
-        <v>3083</v>
-      </c>
-      <c r="H15" t="s">
-        <v>3084</v>
-      </c>
-      <c r="I15" t="s">
-        <v>3085</v>
-      </c>
-      <c r="J15" t="s">
-        <v>3086</v>
-      </c>
-      <c r="K15" t="s">
-        <v>3087</v>
-      </c>
-      <c r="L15" t="s">
-        <v>3088</v>
-      </c>
-      <c r="M15" t="s">
-        <v>3019</v>
-      </c>
-      <c r="N15" t="s">
-        <v>3029</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
-      <c r="A16" t="s">
-        <v>3067</v>
-      </c>
-      <c r="B16" t="s">
-        <v>3068</v>
-      </c>
-      <c r="C16" t="s">
-        <v>3069</v>
-      </c>
-      <c r="D16" t="s">
-        <v>3070</v>
-      </c>
-      <c r="E16" t="s">
-        <v>3071</v>
-      </c>
-      <c r="F16" t="s">
-        <v>3019</v>
-      </c>
-      <c r="G16" t="s">
-        <v>3072</v>
-      </c>
-      <c r="H16" t="s">
-        <v>3073</v>
-      </c>
-      <c r="I16" t="s">
-        <v>3074</v>
-      </c>
-      <c r="J16" t="s">
-        <v>3075</v>
-      </c>
-      <c r="K16" t="s">
-        <v>3076</v>
-      </c>
-      <c r="L16" t="s">
-        <v>3077</v>
-      </c>
-      <c r="M16" t="s">
-        <v>3019</v>
-      </c>
-      <c r="N16" t="s">
-        <v>3029</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
-      <c r="A17" t="s">
-        <v>3019</v>
-      </c>
-      <c r="B17" t="s">
-        <v>3019</v>
-      </c>
-      <c r="C17" t="s">
-        <v>3019</v>
-      </c>
-      <c r="D17" t="s">
-        <v>3019</v>
-      </c>
-      <c r="E17" t="s">
-        <v>3019</v>
-      </c>
-      <c r="F17" t="s">
-        <v>3019</v>
-      </c>
-      <c r="G17" t="s">
-        <v>3019</v>
-      </c>
-      <c r="H17" t="s">
-        <v>3019</v>
-      </c>
-      <c r="I17" t="s">
-        <v>3019</v>
-      </c>
-      <c r="J17" t="s">
-        <v>3019</v>
-      </c>
-      <c r="K17" t="s">
-        <v>3019</v>
-      </c>
-      <c r="L17" t="s">
-        <v>3019</v>
-      </c>
-      <c r="M17" t="s">
-        <v>3019</v>
-      </c>
-      <c r="N17" t="s">
-        <v>3030</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
-      <c r="A18" t="s">
-        <v>3056</v>
-      </c>
-      <c r="B18" t="s">
-        <v>3057</v>
-      </c>
-      <c r="C18" t="s">
-        <v>3058</v>
-      </c>
-      <c r="D18" t="s">
-        <v>3059</v>
-      </c>
-      <c r="E18" t="s">
-        <v>3060</v>
-      </c>
-      <c r="F18" t="s">
-        <v>3019</v>
-      </c>
-      <c r="G18" t="s">
-        <v>3061</v>
-      </c>
-      <c r="H18" t="s">
-        <v>3062</v>
-      </c>
-      <c r="I18" t="s">
-        <v>3063</v>
-      </c>
-      <c r="J18" t="s">
-        <v>3064</v>
-      </c>
-      <c r="K18" t="s">
-        <v>3065</v>
-      </c>
-      <c r="L18" t="s">
-        <v>3066</v>
-      </c>
-      <c r="M18" t="s">
-        <v>3019</v>
-      </c>
-      <c r="N18" t="s">
-        <v>3030</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14">
-      <c r="A19" t="s">
-        <v>3045</v>
-      </c>
-      <c r="B19" t="s">
-        <v>3046</v>
-      </c>
-      <c r="C19" t="s">
-        <v>3047</v>
-      </c>
-      <c r="D19" t="s">
-        <v>3048</v>
-      </c>
-      <c r="E19" t="s">
-        <v>3049</v>
-      </c>
-      <c r="F19" t="s">
-        <v>3019</v>
-      </c>
-      <c r="G19" t="s">
-        <v>3050</v>
-      </c>
-      <c r="H19" t="s">
-        <v>3051</v>
-      </c>
-      <c r="I19" t="s">
-        <v>3052</v>
-      </c>
-      <c r="J19" t="s">
-        <v>3053</v>
-      </c>
-      <c r="K19" t="s">
-        <v>3054</v>
-      </c>
-      <c r="L19" t="s">
-        <v>3055</v>
-      </c>
-      <c r="M19" t="s">
-        <v>3019</v>
-      </c>
-      <c r="N19" t="s">
-        <v>3031</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14">
-      <c r="A20" t="s">
-        <v>3019</v>
-      </c>
-      <c r="B20" t="s">
-        <v>3019</v>
-      </c>
-      <c r="C20" t="s">
-        <v>3019</v>
-      </c>
-      <c r="D20" t="s">
-        <v>3019</v>
-      </c>
-      <c r="E20" t="s">
-        <v>3019</v>
-      </c>
-      <c r="F20" t="s">
-        <v>3019</v>
-      </c>
-      <c r="G20" t="s">
-        <v>3019</v>
-      </c>
-      <c r="H20" t="s">
-        <v>3019</v>
-      </c>
-      <c r="I20" t="s">
-        <v>3019</v>
-      </c>
-      <c r="J20" t="s">
-        <v>3019</v>
-      </c>
-      <c r="K20" t="s">
-        <v>3019</v>
-      </c>
-      <c r="L20" t="s">
-        <v>3019</v>
-      </c>
-      <c r="M20" t="s">
-        <v>3019</v>
-      </c>
-      <c r="N20" t="s">
-        <v>3032</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14">
-      <c r="A21" t="s">
-        <v>3034</v>
-      </c>
-      <c r="B21" t="s">
-        <v>3035</v>
-      </c>
-      <c r="C21" t="s">
-        <v>3036</v>
-      </c>
-      <c r="D21" t="s">
-        <v>3037</v>
-      </c>
-      <c r="E21" t="s">
-        <v>3038</v>
-      </c>
-      <c r="F21" t="s">
-        <v>3019</v>
-      </c>
-      <c r="G21" t="s">
-        <v>3039</v>
-      </c>
-      <c r="H21" t="s">
-        <v>3040</v>
-      </c>
-      <c r="I21" t="s">
-        <v>3041</v>
-      </c>
-      <c r="J21" t="s">
-        <v>3042</v>
-      </c>
-      <c r="K21" t="s">
-        <v>3043</v>
-      </c>
-      <c r="L21" t="s">
-        <v>3044</v>
-      </c>
-      <c r="M21" t="s">
-        <v>3019</v>
-      </c>
-      <c r="N21" t="s">
-        <v>3032</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14">
-      <c r="A22" t="s">
-        <v>3007</v>
-      </c>
-      <c r="B22" t="s">
-        <v>3008</v>
-      </c>
-      <c r="C22" t="s">
-        <v>3009</v>
-      </c>
-      <c r="D22" t="s">
-        <v>3010</v>
-      </c>
-      <c r="E22" t="s">
-        <v>3011</v>
-      </c>
-      <c r="F22" t="s">
-        <v>3019</v>
-      </c>
-      <c r="G22" t="s">
-        <v>3012</v>
-      </c>
-      <c r="H22" t="s">
-        <v>3013</v>
-      </c>
-      <c r="I22" t="s">
-        <v>3014</v>
-      </c>
-      <c r="J22" t="s">
-        <v>3015</v>
-      </c>
-      <c r="K22" t="s">
-        <v>3016</v>
-      </c>
-      <c r="L22" t="s">
-        <v>3017</v>
-      </c>
-      <c r="M22" t="s">
-        <v>3019</v>
-      </c>
-      <c r="N22" t="s">
-        <v>3033</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14">
-      <c r="A23" t="s">
-        <v>3019</v>
-      </c>
-      <c r="B23" t="s">
-        <v>3019</v>
-      </c>
-      <c r="C23" t="s">
-        <v>3019</v>
-      </c>
-      <c r="D23" t="s">
-        <v>3019</v>
-      </c>
-      <c r="E23" t="s">
-        <v>3019</v>
-      </c>
-      <c r="F23" t="s">
-        <v>3019</v>
-      </c>
-      <c r="G23" t="s">
-        <v>3019</v>
-      </c>
-      <c r="H23" t="s">
-        <v>3019</v>
-      </c>
-      <c r="I23" t="s">
-        <v>3019</v>
-      </c>
-      <c r="J23" t="s">
-        <v>3019</v>
-      </c>
-      <c r="K23" t="s">
-        <v>3019</v>
-      </c>
-      <c r="L23" t="s">
-        <v>3019</v>
-      </c>
-      <c r="M23" t="s">
-        <v>3019</v>
-      </c>
-      <c r="N23" t="s">
-        <v>3033</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14">
-      <c r="A24" t="s">
+      <c r="AA44" s="9"/>
+      <c r="AB44" s="9"/>
+      <c r="AC44" s="9"/>
+      <c r="AD44" s="9"/>
+      <c r="AE44" s="9"/>
+      <c r="AF44" s="9"/>
+      <c r="AG44" s="9"/>
+      <c r="AH44" s="9"/>
+      <c r="AI44" s="9"/>
+      <c r="AJ44" s="9"/>
+      <c r="AK44" s="7"/>
+      <c r="AL44" s="5"/>
+      <c r="AM44" s="5"/>
+      <c r="AN44" s="8"/>
+      <c r="AO44" s="8"/>
+    </row>
+    <row r="45" spans="1:41">
+      <c r="A45" s="8" t="s">
         <v>2999</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B45" s="8"/>
+      <c r="C45" s="8"/>
+      <c r="D45" s="8" t="s">
         <v>3000</v>
       </c>
-      <c r="C24" t="s">
+      <c r="E45" s="8"/>
+      <c r="F45" s="8"/>
+      <c r="G45" s="8" t="s">
         <v>3001</v>
       </c>
-      <c r="D24" t="s">
+      <c r="H45" s="8"/>
+      <c r="I45" s="8"/>
+      <c r="J45" s="8" t="s">
         <v>3002</v>
       </c>
-      <c r="E24" t="s">
+      <c r="K45" s="8"/>
+      <c r="L45" s="8"/>
+      <c r="M45" s="8" t="s">
         <v>3003</v>
       </c>
-      <c r="F24" t="s">
+      <c r="N45" s="8"/>
+      <c r="O45" s="8"/>
+      <c r="P45" s="8" t="s">
         <v>3004</v>
       </c>
-      <c r="G24" t="s">
+      <c r="Q45" s="8"/>
+      <c r="R45" s="8"/>
+      <c r="S45" s="8" t="s">
         <v>3005</v>
       </c>
-      <c r="H24" t="s">
+      <c r="T45" s="8"/>
+      <c r="U45" s="8"/>
+      <c r="V45" s="8" t="s">
         <v>3006</v>
       </c>
-      <c r="I24" t="s">
+      <c r="W45" s="8"/>
+      <c r="X45" s="8"/>
+      <c r="Z45" s="9"/>
+      <c r="AA45" s="9"/>
+      <c r="AB45" s="9"/>
+      <c r="AC45" s="9"/>
+      <c r="AD45" s="9"/>
+      <c r="AE45" s="9"/>
+      <c r="AF45" s="9"/>
+      <c r="AG45" s="9"/>
+      <c r="AH45" s="9"/>
+      <c r="AI45" s="9"/>
+      <c r="AJ45" s="9"/>
+      <c r="AK45" s="7"/>
+      <c r="AN45" s="8"/>
+      <c r="AO45" s="8"/>
+    </row>
+    <row r="46" spans="1:41">
+      <c r="A46" s="8"/>
+      <c r="B46" s="8"/>
+      <c r="C46" s="8"/>
+      <c r="D46" s="8"/>
+      <c r="E46" s="8"/>
+      <c r="F46" s="8"/>
+      <c r="G46" s="8"/>
+      <c r="H46" s="8"/>
+      <c r="I46" s="8"/>
+      <c r="J46" s="8"/>
+      <c r="K46" s="8"/>
+      <c r="L46" s="8"/>
+      <c r="M46" s="8"/>
+      <c r="N46" s="8"/>
+      <c r="O46" s="8"/>
+      <c r="P46" s="8"/>
+      <c r="Q46" s="8"/>
+      <c r="R46" s="8"/>
+      <c r="S46" s="8"/>
+      <c r="T46" s="8"/>
+      <c r="U46" s="8"/>
+      <c r="V46" s="8"/>
+      <c r="W46" s="8"/>
+      <c r="X46" s="8"/>
+      <c r="Y46" s="5"/>
+      <c r="Z46" s="9"/>
+      <c r="AA46" s="9"/>
+      <c r="AB46" s="9"/>
+      <c r="AC46" s="9"/>
+      <c r="AD46" s="9"/>
+      <c r="AE46" s="9"/>
+      <c r="AF46" s="9"/>
+      <c r="AG46" s="9"/>
+      <c r="AH46" s="9"/>
+      <c r="AI46" s="9"/>
+      <c r="AJ46" s="9"/>
+      <c r="AK46" s="7"/>
+      <c r="AN46" s="8"/>
+      <c r="AO46" s="8"/>
+    </row>
+    <row r="47" spans="1:41">
+      <c r="Y47" s="5"/>
+      <c r="Z47" s="9"/>
+      <c r="AA47" s="9"/>
+      <c r="AB47" s="9"/>
+      <c r="AC47" s="9"/>
+      <c r="AD47" s="9"/>
+      <c r="AE47" s="9"/>
+      <c r="AF47" s="9"/>
+      <c r="AG47" s="9"/>
+      <c r="AH47" s="9"/>
+      <c r="AI47" s="9"/>
+      <c r="AJ47" s="9"/>
+      <c r="AK47" s="7"/>
+      <c r="AN47" s="8"/>
+      <c r="AO47" s="8"/>
+    </row>
+    <row r="48" spans="1:41">
+      <c r="Y48" s="5"/>
+      <c r="Z48" s="9"/>
+      <c r="AA48" s="9"/>
+      <c r="AB48" s="9"/>
+      <c r="AC48" s="9"/>
+      <c r="AD48" s="9"/>
+      <c r="AE48" s="9"/>
+      <c r="AF48" s="9"/>
+      <c r="AG48" s="9"/>
+      <c r="AH48" s="9"/>
+      <c r="AI48" s="9"/>
+      <c r="AJ48" s="9"/>
+      <c r="AK48" s="7"/>
+      <c r="AL48" s="5"/>
+      <c r="AN48" s="8" t="s">
         <v>3018</v>
       </c>
-      <c r="J24" t="s">
-        <v>3018</v>
-      </c>
-      <c r="K24" t="s">
-        <v>3018</v>
-      </c>
-      <c r="L24" t="s">
-        <v>3018</v>
-      </c>
-      <c r="M24" t="s">
-        <v>3018</v>
-      </c>
-      <c r="N24" t="s">
-        <v>3019</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14">
-      <c r="A25" t="s">
-        <v>3019</v>
-      </c>
-      <c r="B25" t="s">
-        <v>3019</v>
-      </c>
-      <c r="C25" t="s">
-        <v>3019</v>
-      </c>
-      <c r="D25" t="s">
-        <v>3019</v>
-      </c>
-      <c r="E25" t="s">
-        <v>3019</v>
-      </c>
-      <c r="F25" t="s">
-        <v>3019</v>
-      </c>
-      <c r="G25" t="s">
-        <v>3019</v>
-      </c>
-      <c r="H25" t="s">
-        <v>3019</v>
-      </c>
-      <c r="I25" t="s">
-        <v>3018</v>
-      </c>
-      <c r="J25" t="s">
-        <v>3018</v>
-      </c>
-      <c r="K25" t="s">
-        <v>3018</v>
-      </c>
-      <c r="L25" t="s">
-        <v>3018</v>
-      </c>
-      <c r="M25" t="s">
-        <v>3018</v>
-      </c>
-      <c r="N25" t="s">
-        <v>3020</v>
-      </c>
+      <c r="AO48" s="8"/>
+    </row>
+    <row r="49" spans="25:41">
+      <c r="Y49" s="5"/>
+      <c r="Z49" s="9"/>
+      <c r="AA49" s="9"/>
+      <c r="AB49" s="9"/>
+      <c r="AC49" s="9"/>
+      <c r="AD49" s="9"/>
+      <c r="AE49" s="9"/>
+      <c r="AF49" s="9"/>
+      <c r="AG49" s="9"/>
+      <c r="AH49" s="9"/>
+      <c r="AI49" s="9"/>
+      <c r="AJ49" s="9"/>
+      <c r="AK49" s="7"/>
+      <c r="AL49" s="5"/>
+      <c r="AN49" s="8"/>
+      <c r="AO49" s="8"/>
+    </row>
+    <row r="50" spans="25:41">
+      <c r="Y50" s="5"/>
+      <c r="Z50" s="8"/>
+      <c r="AA50" s="8"/>
+      <c r="AB50" s="8"/>
+      <c r="AC50" s="8"/>
+      <c r="AD50" s="8"/>
+      <c r="AE50" s="8"/>
+      <c r="AF50" s="8"/>
+      <c r="AG50" s="8"/>
+      <c r="AH50" s="8"/>
+      <c r="AI50" s="8"/>
+      <c r="AJ50" s="8"/>
+      <c r="AK50" s="6"/>
+      <c r="AL50" s="5"/>
+      <c r="AN50" s="8"/>
+      <c r="AO50" s="8"/>
+    </row>
+    <row r="51" spans="25:41">
+      <c r="Z51" s="6"/>
+      <c r="AA51" s="6"/>
+      <c r="AB51" s="6"/>
+      <c r="AC51" s="6"/>
+      <c r="AD51" s="6"/>
+      <c r="AE51" s="6"/>
+      <c r="AF51" s="6"/>
+      <c r="AG51" s="6"/>
+      <c r="AH51" s="6"/>
+      <c r="AI51" s="6"/>
+      <c r="AJ51" s="6"/>
+      <c r="AK51" s="5"/>
+    </row>
+    <row r="52" spans="25:41">
+      <c r="Z52" s="6"/>
+      <c r="AA52" s="6"/>
+      <c r="AB52" s="6"/>
+      <c r="AC52" s="6"/>
+      <c r="AD52" s="6"/>
+      <c r="AE52" s="6"/>
+      <c r="AF52" s="6"/>
+      <c r="AG52" s="6"/>
+      <c r="AH52" s="6"/>
+      <c r="AI52" s="6"/>
+      <c r="AJ52" s="6"/>
+      <c r="AK52" s="5"/>
+    </row>
+    <row r="53" spans="25:41">
+      <c r="Z53" s="5"/>
+      <c r="AA53" s="5"/>
+      <c r="AB53" s="5"/>
+      <c r="AC53" s="5"/>
+      <c r="AD53" s="5"/>
+      <c r="AE53" s="5"/>
+      <c r="AF53" s="5"/>
+      <c r="AG53" s="5"/>
+      <c r="AH53" s="5"/>
+      <c r="AI53" s="5"/>
+      <c r="AJ53" s="5"/>
+      <c r="AK53" s="5"/>
+    </row>
+    <row r="54" spans="25:41">
+      <c r="Z54" s="5"/>
+      <c r="AA54" s="5"/>
+      <c r="AB54" s="5"/>
+      <c r="AC54" s="5"/>
+      <c r="AD54" s="5"/>
+      <c r="AE54" s="5"/>
+      <c r="AF54" s="5"/>
+      <c r="AG54" s="5"/>
+      <c r="AH54" s="5"/>
+      <c r="AI54" s="5"/>
+      <c r="AJ54" s="5"/>
+      <c r="AK54" s="5"/>
+    </row>
+    <row r="55" spans="25:41">
+      <c r="Z55" s="5"/>
+      <c r="AA55" s="5"/>
+      <c r="AB55" s="5"/>
+      <c r="AC55" s="5"/>
+      <c r="AD55" s="5"/>
+      <c r="AE55" s="5"/>
+      <c r="AF55" s="5"/>
+      <c r="AG55" s="5"/>
+      <c r="AH55" s="5"/>
+      <c r="AI55" s="5"/>
+      <c r="AJ55" s="5"/>
+      <c r="AK55" s="5"/>
+    </row>
+    <row r="56" spans="25:41">
+      <c r="Z56" s="5"/>
+      <c r="AA56" s="5"/>
+      <c r="AB56" s="5"/>
+      <c r="AC56" s="5"/>
+      <c r="AD56" s="5"/>
+      <c r="AE56" s="5"/>
+      <c r="AF56" s="5"/>
+      <c r="AG56" s="5"/>
+      <c r="AH56" s="5"/>
+      <c r="AI56" s="5"/>
+      <c r="AJ56" s="5"/>
+      <c r="AK56" s="5"/>
+    </row>
+    <row r="57" spans="25:41">
+      <c r="Z57" s="5"/>
+      <c r="AA57" s="5"/>
+      <c r="AB57" s="5"/>
+      <c r="AC57" s="5"/>
+      <c r="AD57" s="5"/>
+      <c r="AE57" s="5"/>
+      <c r="AF57" s="5"/>
+      <c r="AG57" s="5"/>
+      <c r="AH57" s="5"/>
+      <c r="AI57" s="5"/>
+      <c r="AJ57" s="5"/>
+      <c r="AK57" s="5"/>
+    </row>
+    <row r="58" spans="25:41">
+      <c r="Z58" s="5"/>
+      <c r="AA58" s="5"/>
+      <c r="AB58" s="5"/>
+      <c r="AC58" s="5"/>
+      <c r="AD58" s="5"/>
+      <c r="AE58" s="5"/>
+      <c r="AF58" s="5"/>
+      <c r="AG58" s="5"/>
+      <c r="AH58" s="5"/>
+      <c r="AI58" s="5"/>
+      <c r="AJ58" s="5"/>
     </row>
   </sheetData>
+  <mergeCells count="161">
+    <mergeCell ref="A37:C38"/>
+    <mergeCell ref="Z44:AJ50"/>
+    <mergeCell ref="C4:L20"/>
+    <mergeCell ref="AH34:AJ35"/>
+    <mergeCell ref="AH37:AJ38"/>
+    <mergeCell ref="AE37:AG38"/>
+    <mergeCell ref="AB37:AD38"/>
+    <mergeCell ref="Y37:AA38"/>
+    <mergeCell ref="V37:X38"/>
+    <mergeCell ref="S37:U38"/>
+    <mergeCell ref="M37:O38"/>
+    <mergeCell ref="J37:L38"/>
+    <mergeCell ref="J32:L33"/>
+    <mergeCell ref="G32:I33"/>
+    <mergeCell ref="D32:F33"/>
+    <mergeCell ref="A32:C33"/>
+    <mergeCell ref="A34:C35"/>
+    <mergeCell ref="D34:F35"/>
+    <mergeCell ref="G34:I35"/>
+    <mergeCell ref="J34:L35"/>
+    <mergeCell ref="M34:O35"/>
+    <mergeCell ref="AE29:AG30"/>
+    <mergeCell ref="AH29:AJ30"/>
+    <mergeCell ref="AH32:AJ33"/>
+    <mergeCell ref="AE32:AG33"/>
+    <mergeCell ref="AB32:AD33"/>
+    <mergeCell ref="Y32:AA33"/>
+    <mergeCell ref="V32:X33"/>
+    <mergeCell ref="S32:U33"/>
+    <mergeCell ref="M32:O33"/>
+    <mergeCell ref="A29:C30"/>
+    <mergeCell ref="D29:F30"/>
+    <mergeCell ref="G29:I30"/>
+    <mergeCell ref="J29:L30"/>
+    <mergeCell ref="M29:O30"/>
+    <mergeCell ref="S29:U30"/>
+    <mergeCell ref="V29:X30"/>
+    <mergeCell ref="Y29:AA30"/>
+    <mergeCell ref="AB29:AD30"/>
+    <mergeCell ref="AH24:AJ25"/>
+    <mergeCell ref="A24:C25"/>
+    <mergeCell ref="D24:F25"/>
+    <mergeCell ref="G24:I25"/>
+    <mergeCell ref="J24:L25"/>
+    <mergeCell ref="M24:O25"/>
+    <mergeCell ref="AH27:AJ28"/>
+    <mergeCell ref="AE27:AG28"/>
+    <mergeCell ref="AB27:AD28"/>
+    <mergeCell ref="Y27:AA28"/>
+    <mergeCell ref="V27:X28"/>
+    <mergeCell ref="S27:U28"/>
+    <mergeCell ref="M27:O28"/>
+    <mergeCell ref="J27:L28"/>
+    <mergeCell ref="G27:I28"/>
+    <mergeCell ref="D27:F28"/>
+    <mergeCell ref="A27:C28"/>
+    <mergeCell ref="Q8:R10"/>
+    <mergeCell ref="Q11:R13"/>
+    <mergeCell ref="Q14:R16"/>
+    <mergeCell ref="Q17:R19"/>
+    <mergeCell ref="AH22:AJ23"/>
+    <mergeCell ref="AE22:AG23"/>
+    <mergeCell ref="AB22:AD23"/>
+    <mergeCell ref="Y22:AA23"/>
+    <mergeCell ref="V22:X23"/>
+    <mergeCell ref="S22:U23"/>
+    <mergeCell ref="S9:U10"/>
+    <mergeCell ref="V9:X10"/>
+    <mergeCell ref="Y9:AA10"/>
+    <mergeCell ref="Y12:AA13"/>
+    <mergeCell ref="V12:X13"/>
+    <mergeCell ref="S12:U13"/>
+    <mergeCell ref="S14:U15"/>
+    <mergeCell ref="V14:X15"/>
+    <mergeCell ref="Y14:AA15"/>
+    <mergeCell ref="S17:U18"/>
+    <mergeCell ref="V17:X18"/>
+    <mergeCell ref="Y17:AA18"/>
+    <mergeCell ref="Y19:AA20"/>
+    <mergeCell ref="V19:X20"/>
+    <mergeCell ref="S19:U20"/>
+    <mergeCell ref="G37:I38"/>
+    <mergeCell ref="D37:F38"/>
+    <mergeCell ref="P33:R33"/>
+    <mergeCell ref="S24:U25"/>
+    <mergeCell ref="V24:X25"/>
+    <mergeCell ref="Y24:AA25"/>
+    <mergeCell ref="AB24:AD25"/>
+    <mergeCell ref="AE24:AG25"/>
+    <mergeCell ref="P38:R38"/>
+    <mergeCell ref="P34:R34"/>
+    <mergeCell ref="S34:U35"/>
+    <mergeCell ref="V34:X35"/>
+    <mergeCell ref="Y34:AA35"/>
+    <mergeCell ref="AB34:AD35"/>
+    <mergeCell ref="AE34:AG35"/>
+    <mergeCell ref="AN3:AO5"/>
+    <mergeCell ref="AN6:AO8"/>
+    <mergeCell ref="AN9:AO11"/>
+    <mergeCell ref="AN12:AO14"/>
+    <mergeCell ref="AE9:AG10"/>
+    <mergeCell ref="AH9:AJ10"/>
+    <mergeCell ref="AH12:AJ13"/>
+    <mergeCell ref="AE12:AG13"/>
+    <mergeCell ref="AE14:AG15"/>
+    <mergeCell ref="AH14:AJ15"/>
+    <mergeCell ref="AE17:AG18"/>
+    <mergeCell ref="AH17:AJ18"/>
+    <mergeCell ref="AH19:AJ20"/>
+    <mergeCell ref="AE19:AG20"/>
+    <mergeCell ref="AN39:AO41"/>
+    <mergeCell ref="AN42:AO44"/>
+    <mergeCell ref="AN45:AO47"/>
+    <mergeCell ref="AN48:AO50"/>
+    <mergeCell ref="AN15:AO17"/>
+    <mergeCell ref="AN18:AO20"/>
+    <mergeCell ref="AN21:AO23"/>
+    <mergeCell ref="AN24:AO26"/>
+    <mergeCell ref="AN27:AO29"/>
+    <mergeCell ref="AN30:AO32"/>
+    <mergeCell ref="AN33:AO35"/>
+    <mergeCell ref="AN36:AO38"/>
+    <mergeCell ref="AB14:AD15"/>
+    <mergeCell ref="AB17:AD18"/>
+    <mergeCell ref="AB19:AD20"/>
+    <mergeCell ref="AB9:AD10"/>
+    <mergeCell ref="AB12:AD13"/>
+    <mergeCell ref="AH39:AJ40"/>
+    <mergeCell ref="P40:R40"/>
+    <mergeCell ref="A39:C40"/>
+    <mergeCell ref="D39:F40"/>
+    <mergeCell ref="G39:I40"/>
+    <mergeCell ref="J39:L40"/>
+    <mergeCell ref="V45:X46"/>
+    <mergeCell ref="S45:U46"/>
+    <mergeCell ref="P45:R46"/>
+    <mergeCell ref="M45:O46"/>
+    <mergeCell ref="J45:L46"/>
+    <mergeCell ref="G45:I46"/>
+    <mergeCell ref="D45:F46"/>
+    <mergeCell ref="A45:C46"/>
+    <mergeCell ref="P39:R39"/>
+    <mergeCell ref="S7:U8"/>
+    <mergeCell ref="V7:X8"/>
+    <mergeCell ref="Y7:AA8"/>
+    <mergeCell ref="AB7:AD8"/>
+    <mergeCell ref="AE7:AG8"/>
+    <mergeCell ref="AH7:AJ8"/>
+    <mergeCell ref="X1:Z2"/>
+    <mergeCell ref="U1:W2"/>
+    <mergeCell ref="R1:T2"/>
+    <mergeCell ref="AJ1:AL2"/>
+    <mergeCell ref="AG1:AI2"/>
+    <mergeCell ref="AD1:AF2"/>
+    <mergeCell ref="AA1:AC2"/>
+    <mergeCell ref="M39:O40"/>
+    <mergeCell ref="S39:U40"/>
+    <mergeCell ref="V39:X40"/>
+    <mergeCell ref="Y39:AA40"/>
+    <mergeCell ref="AB39:AD40"/>
+    <mergeCell ref="AE39:AG40"/>
+  </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
